--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,24 +785,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -810,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +979,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,12 +994,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1056,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1091,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1130,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,12 +1203,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1202,22 +1218,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Academia De Balompie Boliviano -0.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1227,27 +1243,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1288,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,31 +1315,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1331,27 +1355,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1400,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1427,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1418,39 +1442,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1512,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1522,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,110 +1539,870 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6.27945</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>8.616741</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.31576</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>8.616781</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>27.21968</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786116497</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>37.35119</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10.0374</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786116493</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>37.348465</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,46 +539,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,46 +643,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -698,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,12 +754,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +769,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -810,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +851,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +866,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -922,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,27 +963,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1007,26 +987,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -1064,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1146,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1176,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,39 +1179,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1258,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1288,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1298,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1315,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1330,22 +1298,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1370,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1400,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1410,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1427,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1442,12 +1410,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1457,7 +1425,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1467,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1512,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1539,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1554,12 +1522,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1624,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1634,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1651,23 +1619,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1675,7 +1647,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1728,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1738,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1755,12 +1731,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1770,22 +1746,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1795,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1840,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1867,31 +1843,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1899,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1944,17 +1928,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,7 +1955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1979,54 +1963,46 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Real Oruro</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Real Tomayapo vs Real Oruro</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2056,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2066,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2083,31 +2059,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2115,27 +2099,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2160,17 +2144,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2202,12 +2186,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2272,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2282,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2299,110 +2283,1654 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>17.6089</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.3662</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>48.078908</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>33.06999</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.7338</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>45.069833</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>22.48</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>48.085561</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>28.42</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.5913</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>48.067653</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>11.42</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786117945</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>24.427807</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>12.82</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786116567</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>27.718919</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6.27945</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>8.616741</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.31576</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>8.616781</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>27.21968</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786116497</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>37.35119</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>10.0374</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786116493</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>37.348465</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,31 +755,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -779,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,54 +851,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -906,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,28 +955,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,39 +1059,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1107,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,31 +1163,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1226,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,12 +1275,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,39 +1290,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -1338,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1410,22 +1402,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1435,27 +1427,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1522,39 +1514,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -1562,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1634,39 +1626,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -1674,7 +1666,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1723,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,22 +1738,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1771,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,12 +1835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1858,22 +1850,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1883,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,28 +1947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1987,27 +1979,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2024,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,7 +2051,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2067,46 +2059,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -2114,7 +2098,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2144,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2179,46 +2163,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -2226,7 +2202,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2256,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2298,12 +2274,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2313,7 +2289,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2338,7 +2314,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2368,7 +2344,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2354,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,12 +2371,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2410,22 +2386,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2450,7 +2426,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2480,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,27 +2483,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2535,26 +2507,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -2592,7 +2560,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2602,7 +2570,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,12 +2587,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2634,22 +2602,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2674,7 +2642,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2704,7 +2672,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2714,7 +2682,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,39 +2699,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2786,7 +2746,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2816,7 +2776,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2826,7 +2786,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2843,12 +2803,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2858,22 +2818,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2898,7 +2858,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2928,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2938,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2955,7 +2915,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2970,12 +2930,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2985,7 +2945,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2995,27 +2955,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3040,17 +3000,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3067,12 +3027,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3082,12 +3042,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3152,7 +3112,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3162,7 +3122,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3179,23 +3139,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3203,7 +3167,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3256,7 +3224,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3266,7 +3234,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3283,12 +3251,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3298,22 +3266,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3323,27 +3291,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3368,17 +3336,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3395,31 +3363,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3427,27 +3403,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3472,17 +3448,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3499,7 +3475,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3507,54 +3483,46 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Real Oruro</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Real Tomayapo vs Real Oruro</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3584,7 +3552,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3594,7 +3562,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3611,31 +3579,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3643,27 +3619,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3688,17 +3664,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3715,7 +3691,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3730,12 +3706,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3800,7 +3776,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3810,7 +3786,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3827,110 +3803,1654 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>17.6089</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.3662</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>48.078908</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>33.06999</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.7338</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>45.069833</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22.48</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>48.085561</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>28.42</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.5913</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>48.067653</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>11.42</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786117945</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>24.427807</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>12.82</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786116567</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>27.718919</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>6.27945</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>8.616741</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2.31576</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>8.616781</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>27.21968</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786116497</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>37.35119</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10.0374</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786116493</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>37.348465</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -898,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,12 +982,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -987,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,12 +1086,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1091,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,39 +1179,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,39 +1283,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1315,27 +1315,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1514,22 +1514,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1626,22 +1626,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1763,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1850,22 +1850,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,23 +1947,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1971,7 +1975,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2024,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,31 +2059,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2098,7 +2114,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2166,17 +2182,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2187,27 +2203,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2248,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2275,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2267,46 +2283,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -2314,7 +2322,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2344,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2354,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,54 +2379,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,23 +2483,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2507,7 +2511,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2560,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2570,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,7 +2595,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2602,7 +2610,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2672,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,7 +2707,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2710,7 +2718,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2776,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2786,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,12 +2811,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2818,12 +2826,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2888,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,39 +2923,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Real Tomayapo -1</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2955,27 +2955,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3000,17 +3000,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3154,22 +3154,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3179,27 +3179,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3266,22 +3266,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3291,27 +3291,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,7 +3363,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3403,27 +3403,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3475,31 +3475,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3522,7 +3530,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3552,7 +3560,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3562,7 +3570,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3579,7 +3587,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3594,22 +3602,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3619,27 +3627,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3664,17 +3672,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3691,39 +3699,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3731,27 +3731,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,7 +3803,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,7 +3915,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3930,22 +3930,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,7 +4027,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4057,24 +4057,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4139,7 +4139,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4154,22 +4154,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4251,7 +4251,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4490,22 +4490,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -0.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4587,12 +4587,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4602,39 +4602,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4699,31 +4699,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4746,7 +4754,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4776,7 +4784,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4786,7 +4794,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4803,7 +4811,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4818,7 +4826,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4888,7 +4896,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4898,7 +4906,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4915,7 +4923,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4926,7 +4934,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>2.31576</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4992,7 +5000,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5002,7 +5010,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>8.616781</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5019,12 +5027,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5034,22 +5042,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>27.21968</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5059,27 +5067,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5104,17 +5112,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786116497</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>37.35119</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5131,28 +5139,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>10.0374</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5163,27 +5171,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5208,17 +5216,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116493</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>37.348465</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5235,12 +5243,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5250,22 +5258,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5275,27 +5283,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5320,17 +5328,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116236</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>62.947368</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5347,110 +5355,326 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -559,26 +555,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,27 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,31 +659,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
@@ -728,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -787,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +843,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,22 +858,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,31 +955,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1003,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,28 +1067,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1122,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,31 +1171,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1294,12 +1294,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,39 +1387,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1442,7 +1434,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,39 +1491,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1554,7 +1538,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,31 +1603,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1651,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1696,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,12 +1699,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1738,22 +1714,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1778,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,12 +1811,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1850,22 +1826,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1890,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1920,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,12 +1923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1962,22 +1938,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1987,27 +1963,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2008,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,12 +2035,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2074,22 +2050,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2114,7 +2090,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2144,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2179,23 +2155,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2203,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,31 +2259,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2307,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2352,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,31 +2371,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2491,31 +2491,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2523,27 +2515,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2568,17 +2560,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,54 +2587,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -2650,7 +2634,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2680,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2690,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,28 +2691,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2754,7 +2738,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2784,7 +2768,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2778,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,12 +2795,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2826,12 +2810,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2896,7 +2880,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2890,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,7 +2907,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2931,15 +2915,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2947,7 +2935,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3000,7 +2992,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3002,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,27 +3019,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3055,26 +3043,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -3112,7 +3096,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3122,7 +3106,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3139,12 +3123,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3154,22 +3138,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3179,27 +3163,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3224,17 +3208,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3251,27 +3235,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3279,26 +3259,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -3336,7 +3312,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3346,7 +3322,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,7 +3339,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3378,7 +3354,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3448,7 +3424,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3458,7 +3434,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3475,7 +3451,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3490,12 +3466,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3560,7 +3536,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3570,7 +3546,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3587,7 +3563,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3602,22 +3578,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3627,27 +3603,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3672,17 +3648,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,31 +3675,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3731,27 +3715,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3776,17 +3760,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,7 +3787,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3818,22 +3802,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3843,27 +3827,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3888,17 +3872,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,7 +3899,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3930,22 +3914,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3955,27 +3939,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4000,17 +3984,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,39 +4011,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano 0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4067,27 +4043,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4112,17 +4088,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4139,7 +4115,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4154,22 +4130,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4194,7 +4170,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4224,7 +4200,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4234,7 +4210,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4251,7 +4227,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4266,12 +4242,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4336,7 +4312,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4346,7 +4322,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4363,7 +4339,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4378,22 +4354,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano 0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4418,7 +4394,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4448,7 +4424,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4458,7 +4434,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4475,7 +4451,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4490,22 +4466,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4530,7 +4506,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4560,7 +4536,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4570,7 +4546,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4587,12 +4563,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4602,22 +4578,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4642,7 +4618,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4672,7 +4648,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4682,7 +4658,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4699,7 +4675,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4714,12 +4690,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4784,7 +4760,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4794,7 +4770,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4811,12 +4787,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4826,39 +4802,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4866,7 +4842,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4896,7 +4872,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4906,7 +4882,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4923,31 +4899,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4970,7 +4954,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5000,7 +4984,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5010,7 +4994,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5027,12 +5011,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5042,39 +5026,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -5082,7 +5066,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5112,7 +5096,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5122,7 +5106,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5139,7 +5123,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5147,15 +5131,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5163,7 +5151,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5216,7 +5208,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5226,7 +5218,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5243,39 +5235,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>2.31576</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5283,27 +5267,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5328,17 +5312,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>8.616781</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5355,31 +5339,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>27.21968</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5387,27 +5379,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5432,17 +5424,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116497</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>37.35119</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5459,27 +5451,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>10.0374</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5487,26 +5475,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -5544,7 +5528,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116493</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5554,7 +5538,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>37.348465</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5571,110 +5555,438 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,23 +643,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aurora +0.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,12 +758,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,12 +851,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -858,22 +866,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -883,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -970,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo -1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -995,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,28 +1075,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1099,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1186,22 +1194,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1211,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,23 +1299,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo -0.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1315,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1395,23 +1411,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1419,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1464,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1499,23 +1523,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo 0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1523,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1600,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,23 +1635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1627,27 +1667,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1712,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,12 +1739,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1714,22 +1754,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1739,27 +1779,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1824,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,12 +1851,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1826,22 +1866,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>San Antonio Bulo Bulo +0.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1851,27 +1891,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1936,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,7 +1963,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1938,22 +1978,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1963,27 +2003,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +2048,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,7 +2075,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2043,31 +2083,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2075,27 +2107,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2152,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2179,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2155,31 +2187,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2187,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2256,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,27 +2283,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2287,11 +2307,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Nacional Potosí</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2299,27 +2315,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2360,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,12 +2387,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2386,22 +2402,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2411,27 +2427,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2456,17 +2472,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,23 +2499,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2507,7 +2527,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2515,27 +2539,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2560,17 +2584,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,28 +2611,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2634,7 +2658,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2664,7 +2688,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,31 +2715,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2738,7 +2770,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2768,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2778,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,7 +2827,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2803,31 +2835,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2835,27 +2859,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2880,17 +2904,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2907,54 +2931,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -2962,7 +2978,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2992,7 +3008,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3002,7 +3018,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3019,28 +3035,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3066,7 +3082,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3096,7 +3112,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3106,7 +3122,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3123,39 +3139,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3163,27 +3171,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3208,17 +3216,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,31 +3243,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3282,7 +3298,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3312,7 +3328,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3338,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,12 +3355,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3354,39 +3370,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -3394,7 +3410,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3424,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3434,7 +3450,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3451,7 +3467,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3466,22 +3482,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3491,27 +3507,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3536,17 +3552,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,7 +3579,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3578,39 +3594,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -3618,7 +3634,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3648,7 +3664,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3658,7 +3674,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3675,7 +3691,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3690,39 +3706,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -3730,7 +3746,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3760,7 +3776,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3770,7 +3786,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3787,12 +3803,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3802,22 +3818,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3827,27 +3843,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3872,17 +3888,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3899,12 +3915,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3914,22 +3930,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3939,27 +3955,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3984,17 +4000,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4011,28 +4027,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4043,27 +4059,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4088,17 +4104,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4115,7 +4131,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4123,46 +4139,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4170,7 +4178,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4200,7 +4208,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4210,7 +4218,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4227,7 +4235,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4235,46 +4243,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4451,12 +4451,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4563,27 +4563,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4591,26 +4587,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4648,7 +4640,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4658,7 +4650,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4675,12 +4667,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4690,22 +4682,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4730,7 +4722,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4760,7 +4752,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4770,7 +4762,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4787,39 +4779,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4842,7 +4826,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4872,7 +4856,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4882,7 +4866,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4899,12 +4883,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4914,22 +4898,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4954,7 +4938,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4984,7 +4968,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4994,7 +4978,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5011,7 +4995,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5026,12 +5010,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5041,7 +5025,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5051,27 +5035,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5096,17 +5080,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5123,12 +5107,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5138,12 +5122,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5208,7 +5192,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5218,7 +5202,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5235,23 +5219,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5259,7 +5247,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5312,7 +5304,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5322,7 +5314,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5339,12 +5331,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5354,22 +5346,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5379,27 +5371,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5424,17 +5416,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5451,31 +5443,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5483,27 +5483,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5528,17 +5528,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5555,7 +5555,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5563,54 +5563,46 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Real Oruro</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Real Tomayapo vs Real Oruro</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5640,7 +5632,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5650,7 +5642,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5667,31 +5659,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5699,27 +5699,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5744,17 +5744,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5883,110 +5883,1654 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>17.6089</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.3662</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>48.078908</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>33.06999</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.7338</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>45.069833</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22.48</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>48.085561</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28.42</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.5913</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>48.067653</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>11.42</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786117945</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>24.427807</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>12.82</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786116567</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>27.718919</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6.27945</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>8.616741</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2.31576</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>8.616781</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>27.21968</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786116497</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>37.35119</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>10.0374</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786116493</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>37.348465</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,39 +643,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Aurora +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -866,12 +874,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -881,7 +889,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora 0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -891,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -978,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -1</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1003,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,23 +1083,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1099,7 +1111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1122,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1234,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,31 +1315,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1346,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,27 +1411,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1431,11 +1435,7 @@
           <t>Asian Handicap (0.5)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1443,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>Aurora +0.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1555,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,54 +1627,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -1682,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1712,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1722,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,12 +1731,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1754,17 +1746,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1794,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1824,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1834,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1866,22 +1858,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo -1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1906,7 +1898,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1936,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1946,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1963,7 +1955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1971,46 +1963,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -2018,7 +2002,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2048,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2058,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,7 +2059,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,23 +2067,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo -0.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2107,27 +2099,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2152,17 +2144,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2187,23 +2179,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo -0.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2211,27 +2211,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,31 +2283,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2315,27 +2323,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,17 +2368,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,12 +2395,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2402,22 +2410,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo 0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2427,27 +2435,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,17 +2480,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,12 +2507,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2514,22 +2522,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2539,27 +2547,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2584,17 +2592,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,31 +2619,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2643,27 +2659,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2688,17 +2704,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,12 +2731,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2730,22 +2746,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>San Antonio Bulo Bulo +0.5</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2755,27 +2771,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2800,17 +2816,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,7 +2843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2835,23 +2851,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2859,27 +2883,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2904,17 +2928,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,7 +2955,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2942,17 +2966,17 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2963,27 +2987,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3008,17 +3032,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,7 +3059,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3046,17 +3070,17 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3067,27 +3091,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3112,17 +3136,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3139,28 +3163,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3171,27 +3195,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3216,17 +3240,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3243,12 +3267,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3258,22 +3282,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3283,27 +3307,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3328,17 +3352,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3355,12 +3379,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3370,22 +3394,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3395,27 +3419,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3440,17 +3464,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3467,39 +3491,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3522,7 +3538,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3552,7 +3568,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3562,7 +3578,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3579,12 +3595,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3594,22 +3610,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Academia De Balompie Boliviano -1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3634,7 +3650,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3664,7 +3680,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3674,7 +3690,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3691,7 +3707,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3699,19 +3715,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3719,11 +3731,7 @@
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3731,27 +3739,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3776,17 +3784,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,39 +3811,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Nacional Potosí</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3843,27 +3843,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,39 +3915,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3970,7 +3962,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4000,7 +3992,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4010,7 +4002,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,7 +4019,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4038,17 +4030,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4059,27 +4051,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4104,17 +4096,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4131,31 +4123,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4235,31 +4235,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4282,7 +4290,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4312,7 +4320,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4322,7 +4330,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4339,7 +4347,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4354,39 +4362,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4394,7 +4402,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4424,7 +4432,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4434,7 +4442,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4451,12 +4459,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4466,39 +4474,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -4506,7 +4514,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4536,7 +4544,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4546,7 +4554,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4563,31 +4571,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4610,7 +4626,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4640,7 +4656,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4650,7 +4666,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4667,12 +4683,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4682,22 +4698,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4707,27 +4723,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4752,17 +4768,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4779,31 +4795,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4826,7 +4850,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4856,7 +4880,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4866,7 +4890,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4883,7 +4907,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4891,31 +4915,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4923,27 +4939,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4968,17 +4984,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4995,7 +5011,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5003,31 +5019,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Real Tomayapo -1</t>
-        </is>
-      </c>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5035,27 +5043,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5080,17 +5088,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5107,7 +5115,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5115,46 +5123,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5331,12 +5331,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5346,22 +5346,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5371,27 +5371,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5416,17 +5416,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5443,39 +5443,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Real Tomayapo -1</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5483,27 +5475,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5528,17 +5520,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5555,31 +5547,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5587,27 +5587,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5659,27 +5659,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5687,26 +5683,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -5744,7 +5736,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5754,7 +5746,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5771,7 +5763,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5786,12 +5778,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5856,7 +5848,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5866,7 +5858,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5883,7 +5875,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5898,22 +5890,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5923,27 +5915,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5968,17 +5960,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5995,7 +5987,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6010,22 +6002,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6050,7 +6042,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6080,7 +6072,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6090,7 +6082,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6107,7 +6099,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6122,12 +6114,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6192,7 +6184,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6202,7 +6194,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6219,7 +6211,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6234,12 +6226,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6249,7 +6241,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6259,27 +6251,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6304,17 +6296,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6331,7 +6323,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6346,22 +6338,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6371,27 +6363,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6416,17 +6408,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6443,39 +6435,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6483,27 +6467,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6528,17 +6512,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6555,7 +6539,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6570,22 +6554,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6610,7 +6594,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6640,7 +6624,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6650,7 +6634,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6667,12 +6651,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6682,12 +6666,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6752,7 +6736,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6762,7 +6746,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6779,23 +6763,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6803,7 +6791,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6826,7 +6818,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6856,7 +6848,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6866,7 +6858,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6883,12 +6875,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6898,39 +6890,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6938,7 +6930,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6968,7 +6960,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6978,7 +6970,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6995,23 +6987,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7019,7 +7015,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7099,12 +7099,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7114,22 +7114,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Academia De Balompie Boliviano -1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7139,27 +7139,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7184,17 +7184,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7211,31 +7211,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7243,27 +7251,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7288,17 +7296,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7315,12 +7323,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7330,39 +7338,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7370,7 +7378,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7400,7 +7408,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7410,7 +7418,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7427,110 +7435,982 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>12.82</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786116567</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>27.718919</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>6.27945</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>8.616741</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2.31576</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>8.616781</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>27.21968</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786116497</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>37.35119</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>10.0374</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786116493</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>37.348465</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
+          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.95088</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786215586</t>
+          <t>1786221634</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>48.540878</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
+          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.18362</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
+          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786215460</t>
+          <t>1786220197</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>23.179991</t>
+          <t>48.498994</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
+          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,31 +755,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -787,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786215452</t>
+          <t>1786220102</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>11.209581</t>
+          <t>138.88</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +866,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.24912</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aurora 0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.069128</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,54 +963,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Aurora vs Club Bolivar</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Aurora vs Club Bolivar</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Club Bolivar</t>
@@ -1026,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>36.862275</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.8877</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786215147</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1194,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora 0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786214770</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>43.961538</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1315,23 +1299,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1339,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786211480</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>8.297872</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,31 +1403,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1443,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aurora +0.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1555,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,28 +1627,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,39 +1731,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1771,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1858,22 +1850,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -1</t>
+          <t>Aurora +0.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1883,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,23 +1947,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2032,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,12 +2051,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2074,22 +2066,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2114,7 +2106,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2144,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2146,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,7 +2163,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2186,22 +2178,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
+          <t>San Antonio Bulo Bulo -1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2226,7 +2218,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2256,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,7 +2275,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2291,14 +2283,10 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2308,14 +2296,10 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2338,7 +2322,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2378,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,7 +2379,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2410,22 +2394,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2450,7 +2434,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2490,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,7 +2491,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2522,39 +2506,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo -0.5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -2562,7 +2546,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2602,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,7 +2603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2634,39 +2618,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -2674,7 +2658,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2714,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2731,7 +2715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2746,22 +2730,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo 0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2786,7 +2770,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2816,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2826,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2843,7 +2827,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2858,12 +2842,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2928,7 +2912,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2938,7 +2922,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2955,7 +2939,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2963,15 +2947,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2979,7 +2967,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2987,27 +2979,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3017,7 +3009,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3032,17 +3024,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3059,7 +3051,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3067,23 +3059,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3091,27 +3091,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3136,17 +3136,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3163,31 +3163,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3195,27 +3203,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3240,17 +3248,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3267,27 +3275,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3295,26 +3299,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3379,27 +3379,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3407,31 +3403,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
@@ -3464,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3474,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3491,28 +3483,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3523,27 +3515,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3568,17 +3560,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,12 +3587,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3610,22 +3602,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3635,27 +3627,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3680,17 +3672,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3707,31 +3699,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3739,27 +3739,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3784,17 +3784,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3811,28 +3811,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,31 +3915,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3962,7 +3970,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3992,7 +4000,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4002,7 +4010,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4019,7 +4027,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4030,12 +4038,12 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4096,7 +4104,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4106,7 +4114,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4123,39 +4131,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4235,39 +4235,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4290,7 +4282,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4320,7 +4312,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4330,7 +4322,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4347,7 +4339,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4355,31 +4347,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4387,27 +4371,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4432,17 +4416,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4459,12 +4443,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4474,22 +4458,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4514,7 +4498,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4544,7 +4528,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4554,7 +4538,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4571,12 +4555,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4586,22 +4570,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4626,7 +4610,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4656,7 +4640,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4666,7 +4650,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4683,12 +4667,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4698,22 +4682,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4723,27 +4707,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4768,17 +4752,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4795,12 +4779,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4810,22 +4794,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4850,7 +4834,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4880,7 +4864,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4890,7 +4874,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4907,7 +4891,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4915,23 +4899,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4939,27 +4931,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4984,17 +4976,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5011,31 +5003,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5043,27 +5043,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5115,31 +5115,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5162,7 +5170,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5192,7 +5200,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5202,7 +5210,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5219,7 +5227,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5227,31 +5235,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5259,27 +5259,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5331,54 +5331,46 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -5386,7 +5378,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5416,7 +5408,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5426,7 +5418,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5443,28 +5435,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5490,7 +5482,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5520,7 +5512,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5530,7 +5522,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5547,12 +5539,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5562,12 +5554,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5632,7 +5624,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5642,7 +5634,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5659,7 +5651,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5667,15 +5659,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5683,7 +5679,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5763,27 +5763,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5791,26 +5787,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -5848,7 +5840,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5858,7 +5850,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5875,12 +5867,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5890,22 +5882,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5915,27 +5907,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5960,17 +5952,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5987,27 +5979,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6015,26 +6003,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6072,7 +6056,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6082,7 +6066,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6099,7 +6083,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6114,7 +6098,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6184,7 +6168,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6194,7 +6178,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6211,7 +6195,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6226,12 +6210,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6296,7 +6280,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6306,7 +6290,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6323,7 +6307,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6338,22 +6322,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6363,27 +6347,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6408,17 +6392,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6435,31 +6419,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6467,27 +6459,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6512,17 +6504,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6539,7 +6531,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6554,22 +6546,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6579,27 +6571,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6624,17 +6616,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6651,7 +6643,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6666,22 +6658,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6691,27 +6683,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6736,17 +6728,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6763,39 +6755,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano 0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6803,27 +6787,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6848,17 +6832,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6875,7 +6859,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6890,22 +6874,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6930,7 +6914,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6960,7 +6944,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6970,7 +6954,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6987,7 +6971,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7002,12 +6986,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7072,7 +7056,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7082,7 +7066,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7099,7 +7083,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7114,22 +7098,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano 0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7154,7 +7138,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7184,7 +7168,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7194,7 +7178,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7211,7 +7195,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7226,22 +7210,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7266,7 +7250,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7296,7 +7280,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7306,7 +7290,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7323,12 +7307,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7338,22 +7322,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7378,7 +7362,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7408,7 +7392,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7418,7 +7402,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7435,7 +7419,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7450,12 +7434,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7520,7 +7504,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7530,7 +7514,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7547,12 +7531,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7562,39 +7546,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7602,7 +7586,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7632,7 +7616,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7642,7 +7626,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7659,31 +7643,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7706,7 +7698,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7736,7 +7728,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7746,7 +7738,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7763,12 +7755,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7778,39 +7770,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7818,7 +7810,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7848,7 +7840,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7858,7 +7850,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7875,7 +7867,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7883,15 +7875,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7899,7 +7895,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7979,39 +7979,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>2.31576</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8019,27 +8011,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8064,17 +8056,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>8.616781</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8091,31 +8083,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>27.21968</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8123,27 +8123,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8168,17 +8168,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116497</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>37.35119</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8195,27 +8195,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>10.0374</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8223,26 +8219,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8280,7 +8272,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116493</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8290,7 +8282,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>37.348465</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8307,110 +8299,438 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
+          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>32.21729</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.6913</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786221634</t>
+          <t>1786232638</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>46.607291</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
+          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +643,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>27.56875</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
+          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786220197</t>
+          <t>1786232521</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.498994</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
+          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -758,17 +750,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>26.79929</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786220102</t>
+          <t>1786230822</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>47.749292</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
+          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,31 +851,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.95088</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786215586</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.540878</t>
+          <t>48.536913</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,28 +947,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
+          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.18362</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1010,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786215460</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>23.179991</t>
+          <t>47.786192</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
+          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1075,46 +1059,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Aurora vs Club Bolivar</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Aurora vs Club Bolivar</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Club Bolivar</t>
@@ -1122,7 +1098,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1128,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786215452</t>
+          <t>1786227616</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11.209581</t>
+          <t>4.833333</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,39 +1155,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
+          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20.24912</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Aurora 0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1219,27 +1187,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1232,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786221634</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.069128</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1259,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
+          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1306,22 +1274,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1331,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786220197</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36.862275</t>
+          <t>48.498994</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,39 +1371,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
+          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.8877</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1458,7 +1418,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1473,7 +1433,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1488,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786215147</t>
+          <t>1786220102</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>138.88</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1475,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,22 +1490,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1570,7 +1530,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1585,7 +1545,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1600,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786214770</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>43.961538</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,28 +1587,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1659,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786211480</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>8.297872</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,31 +1691,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1778,7 +1746,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1850,22 +1818,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aurora +0.5</t>
+          <t>Aurora 0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1890,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1920,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,31 +1915,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1979,27 +1955,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2024,17 +2000,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,12 +2027,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2066,39 +2042,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -2106,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2121,7 +2097,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2136,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,12 +2139,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2178,22 +2154,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2218,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2233,7 +2209,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2248,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2258,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2286,17 +2262,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2322,7 +2298,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2352,7 +2328,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2362,7 +2338,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,39 +2355,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2419,27 +2387,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2464,17 +2432,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,7 +2459,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2506,22 +2474,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
+          <t>Aurora +0.5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2531,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2576,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,39 +2571,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2658,7 +2618,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2688,7 +2648,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2658,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,12 +2675,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2730,12 +2690,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2745,7 +2705,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2770,7 +2730,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2800,7 +2760,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2770,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,7 +2787,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2842,39 +2802,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo -1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -2882,7 +2842,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2912,7 +2872,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2882,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,7 +2899,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2947,19 +2907,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2967,26 +2923,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -2994,7 +2946,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3009,7 +2961,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3051,7 +3003,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3066,22 +3018,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3106,7 +3058,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3136,7 +3088,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3146,7 +3098,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3163,7 +3115,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3178,39 +3130,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo -0.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3218,7 +3170,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3248,7 +3200,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3258,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3275,7 +3227,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3283,23 +3235,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3307,27 +3267,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3352,17 +3312,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3379,7 +3339,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3387,23 +3347,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo 0</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3411,27 +3379,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3456,17 +3424,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,31 +3451,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3515,27 +3491,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3560,17 +3536,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3587,12 +3563,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3602,12 +3578,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3617,7 +3593,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3627,27 +3603,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3657,7 +3633,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3672,17 +3648,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,12 +3675,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3714,22 +3690,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo +0.5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3739,27 +3715,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3784,17 +3760,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3811,31 +3787,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3843,27 +3827,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3888,17 +3872,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3915,39 +3899,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3955,27 +3931,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4000,17 +3976,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4027,7 +4003,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4038,17 +4014,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4059,27 +4035,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4104,17 +4080,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4131,28 +4107,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4163,27 +4139,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4208,17 +4184,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4235,31 +4211,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4267,27 +4251,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4312,17 +4296,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4339,31 +4323,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4371,27 +4363,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4416,17 +4408,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4443,7 +4435,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4451,31 +4443,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4498,7 +4482,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4528,7 +4512,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4538,7 +4522,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4555,7 +4539,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4570,22 +4554,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Academia De Balompie Boliviano -1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4610,7 +4594,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4640,7 +4624,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4650,7 +4634,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4667,7 +4651,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4675,31 +4659,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4707,27 +4683,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4752,17 +4728,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4779,7 +4755,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4787,31 +4763,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4834,7 +4802,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4864,7 +4832,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4874,7 +4842,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4891,7 +4859,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4899,19 +4867,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4919,11 +4883,7 @@
           <t>Under/Over (3)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4976,7 +4936,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4986,7 +4946,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5003,39 +4963,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Nacional Potosí</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5043,27 +4995,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5088,17 +5040,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5115,7 +5067,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5135,7 +5087,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5200,7 +5152,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5210,7 +5162,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5227,31 +5179,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5259,27 +5219,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5304,17 +5264,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5331,7 +5291,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5339,23 +5299,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5378,7 +5346,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5408,7 +5376,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5418,7 +5386,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5435,7 +5403,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5443,23 +5411,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5482,7 +5458,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5512,7 +5488,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5522,7 +5498,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5539,7 +5515,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5554,39 +5530,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -5594,7 +5570,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5624,7 +5600,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5634,7 +5610,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5651,12 +5627,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5666,22 +5642,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5691,27 +5667,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5736,17 +5712,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5763,31 +5739,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5810,7 +5794,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5840,7 +5824,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5850,7 +5834,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5867,39 +5851,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5907,27 +5883,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5952,17 +5928,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5979,28 +5955,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6026,7 +6002,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6056,7 +6032,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6066,7 +6042,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6083,7 +6059,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6091,46 +6067,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6138,7 +6106,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6168,7 +6136,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6178,7 +6146,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6195,7 +6163,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6210,22 +6178,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6235,27 +6203,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6280,17 +6248,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6307,12 +6275,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6322,12 +6290,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6392,7 +6360,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6402,7 +6370,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6419,27 +6387,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6447,26 +6411,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6504,7 +6464,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6514,7 +6474,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6531,12 +6491,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6546,22 +6506,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6571,27 +6531,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6616,17 +6576,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6643,39 +6603,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Real Tomayapo -1</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6683,27 +6635,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6728,17 +6680,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6755,31 +6707,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6787,27 +6747,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6832,17 +6792,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6859,7 +6819,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6874,22 +6834,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6899,27 +6859,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6944,17 +6904,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6971,7 +6931,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6986,12 +6946,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7056,7 +7016,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7066,7 +7026,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7083,7 +7043,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7098,12 +7058,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7113,7 +7073,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7138,7 +7098,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7168,7 +7128,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7178,7 +7138,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7195,7 +7155,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7210,22 +7170,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7235,27 +7195,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7280,17 +7240,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7307,7 +7267,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7322,22 +7282,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7347,27 +7307,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7392,17 +7352,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7419,39 +7379,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7459,27 +7411,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7504,17 +7456,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7531,7 +7483,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7546,22 +7498,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7586,7 +7538,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7616,7 +7568,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7626,7 +7578,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7643,12 +7595,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7658,22 +7610,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7698,7 +7650,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7728,7 +7680,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7738,7 +7690,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7755,7 +7707,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7770,22 +7722,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano 0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7810,7 +7762,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7840,7 +7792,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7850,7 +7802,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7867,12 +7819,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7882,39 +7834,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7922,7 +7874,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7952,7 +7904,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7962,7 +7914,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7979,23 +7931,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8003,7 +7959,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8056,7 +8016,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8066,7 +8026,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8083,12 +8043,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8098,39 +8058,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8138,7 +8098,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8168,7 +8128,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8178,7 +8138,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8195,31 +8155,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8242,7 +8210,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8272,7 +8240,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8282,7 +8250,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8299,12 +8267,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8314,22 +8282,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Academia De Balompie Boliviano -1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8339,27 +8307,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8384,17 +8352,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8411,31 +8379,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8443,27 +8419,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8488,17 +8464,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8515,12 +8491,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8530,12 +8506,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8600,7 +8576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8610,7 +8586,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8627,110 +8603,758 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2.31576</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>8.616781</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>27.21968</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1786116497</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>37.35119</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>10.0374</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1786116493</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>37.348465</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V82"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
+          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.21729</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6913</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
+          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786232638</t>
+          <t>1786234428</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>46.607291</t>
+          <t>14.281124</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
+          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,17 +654,17 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.56875</t>
+          <t>32.21729</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6913</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786232521</t>
+          <t>1786232638</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>46.607291</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
+          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,17 +758,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.79929</t>
+          <t>27.56875</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786230822</t>
+          <t>1786232521</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>47.749292</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
+          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,12 +862,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>26.79929</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786230822</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>48.536913</t>
+          <t>47.749292</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
+          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,12 +966,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -994,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1034,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>47.786192</t>
+          <t>48.536913</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
+          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1062,17 +1070,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1098,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1128,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786227616</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4.833333</t>
+          <t>47.786192</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,28 +1163,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
+          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1187,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1232,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786221634</t>
+          <t>1786227616</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>4.833333</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,39 +1267,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
+          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1299,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786220197</t>
+          <t>1786221634</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>48.498994</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
+          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1379,23 +1379,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1403,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1448,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786220102</t>
+          <t>1786220197</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>48.498994</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
+          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1483,31 +1491,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.95088</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786215586</t>
+          <t>1786220102</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.540878</t>
+          <t>138.88</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,31 +1587,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.18362</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1619,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786215460</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>23.179991</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,54 +1699,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aurora vs Club Bolivar</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Aurora vs Club Bolivar</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Club Bolivar</t>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786215452</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>11.209581</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.24912</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aurora 0</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.069128</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Aurora 0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Aurora vs Club Bolivar</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Aurora vs Club Bolivar</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Club Bolivar</t>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>36.862275</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,22 +2042,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.8877</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2067,27 +2067,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786215147</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786214770</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>43.961538</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,31 +2251,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2298,7 +2306,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2313,7 +2321,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2328,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786211480</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2338,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>8.297872</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,28 +2363,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2387,27 +2395,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2440,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,27 +2467,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2487,11 +2491,7 @@
           <t>Asian Handicap (0.5)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Aurora +0.5</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,31 +2571,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Aurora +0.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2603,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2648,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,7 +2683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2683,46 +2691,38 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,12 +2787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -1</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2907,23 +2907,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo -1</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2946,7 +2954,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +2984,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +2994,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,7 +3011,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3011,31 +3019,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,7 +3227,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3242,22 +3242,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,7 +3339,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3354,22 +3354,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>San Antonio Bulo Bulo +0.5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3451,7 +3451,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3481,24 +3481,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo 0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3578,17 +3578,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3675,7 +3675,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3690,22 +3690,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3787,7 +3787,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3802,39 +3802,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3899,7 +3899,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3907,23 +3907,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3931,27 +3939,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3976,17 +3984,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4003,7 +4011,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4014,12 +4022,12 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4050,7 +4058,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4080,7 +4088,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4090,7 +4098,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4107,23 +4115,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4154,7 +4162,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4184,7 +4192,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4194,7 +4202,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4211,27 +4219,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4239,26 +4243,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4323,12 +4323,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4353,32 +4353,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>Independiente Petrolero</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4435,31 +4435,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4467,27 +4475,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4512,17 +4520,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4539,7 +4547,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4547,31 +4555,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,31 +4651,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4683,27 +4691,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4728,17 +4736,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,7 +4763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4766,12 +4774,12 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4787,27 +4795,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4832,17 +4840,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4859,7 +4867,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4870,7 +4878,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4936,7 +4944,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4946,7 +4954,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4963,7 +4971,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4974,12 +4982,12 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4995,27 +5003,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5040,17 +5048,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5067,39 +5075,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5107,27 +5107,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5152,17 +5152,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,12 +5291,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5403,7 +5403,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5418,22 +5418,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5515,7 +5515,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5530,22 +5530,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5627,12 +5627,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5642,22 +5642,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5667,27 +5667,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5712,17 +5712,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5739,12 +5739,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5754,22 +5754,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5779,27 +5779,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5824,17 +5824,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5851,31 +5851,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5883,27 +5891,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5928,17 +5936,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5955,7 +5963,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5966,17 +5974,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5987,27 +5995,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6032,17 +6040,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6059,7 +6067,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6070,12 +6078,12 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6136,7 +6144,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6146,7 +6154,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6163,7 +6171,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6171,46 +6179,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6275,12 +6275,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6387,7 +6387,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6395,15 +6395,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6411,7 +6415,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6474,7 +6482,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6491,7 +6499,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6499,19 +6507,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6519,26 +6523,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6611,15 +6611,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6627,7 +6631,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6690,7 +6698,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6707,27 +6715,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6735,26 +6739,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6834,22 +6834,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6859,27 +6859,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6946,22 +6946,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6971,27 +6971,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7043,7 +7043,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7155,7 +7155,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7195,27 +7195,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7240,17 +7240,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7267,7 +7267,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7379,31 +7379,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7426,7 +7434,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7456,7 +7464,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7466,7 +7474,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7483,39 +7491,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7523,27 +7523,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7568,17 +7568,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7610,12 +7610,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7707,7 +7707,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7819,7 +7819,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7834,22 +7834,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano 0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7931,7 +7931,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7946,39 +7946,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8043,7 +8043,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8058,22 +8058,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8170,22 +8170,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano -1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8267,12 +8267,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8282,22 +8282,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -0.5</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8379,12 +8379,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8491,12 +8491,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8506,39 +8506,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8603,7 +8603,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8611,15 +8611,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8627,7 +8631,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8690,7 +8698,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8707,7 +8715,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8715,19 +8723,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>2.31576</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8735,26 +8739,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>8.616781</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8819,7 +8819,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8827,15 +8827,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>27.21968</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8843,7 +8847,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8896,7 +8904,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786116497</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8906,7 +8914,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>37.35119</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8923,39 +8931,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>10.0374</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8963,27 +8963,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -9008,17 +9008,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786116493</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>37.348465</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9035,7 +9035,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9043,15 +9043,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9059,7 +9063,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9082,7 +9090,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9112,7 +9120,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116236</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9122,7 +9130,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>62.947368</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9139,39 +9147,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9179,27 +9179,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9224,17 +9224,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116231</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>79.82266</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9251,110 +9251,222 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V83"/>
+  <dimension ref="A1:V85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
+          <t>0x99d108064ee486a128c0f102cc16036611e7fb652eb8c6a0f2c32f5b772f89fc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
+          <t>0x3b1faf5c1f9c937e6fcae3ef58467801391c1a89415ceb56bda0f3d6b89fad5a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786234428</t>
+          <t>1786239678</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14.281124</t>
+          <t>1.918465</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
+          <t>0xfc58591c771627eb6a429bb634826daa1107a573e96c81b60c2a93d505d40222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,23 +643,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.21729</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6913</t>
+          <t>1.2237</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
+          <t>0x09e87d20acf35e835c5573176b05437997818c183e7c5ce4737e4924e58830f6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786232638</t>
+          <t>1786239045</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>46.607291</t>
+          <t>25.519553</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
+          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27.56875</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -794,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
+          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786232521</t>
+          <t>1786234428</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>14.281124</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
+          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,17 +870,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26.79929</t>
+          <t>32.21729</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.6913</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786230822</t>
+          <t>1786232638</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>47.749292</t>
+          <t>46.607291</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
+          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,17 +974,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.56875</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -987,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786232521</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>48.536913</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
+          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,7 +1078,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.79929</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1106,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786230822</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>47.786192</t>
+          <t>47.749292</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
+          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1174,17 +1182,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1210,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786227616</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.833333</t>
+          <t>48.536913</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,28 +1275,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
+          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1299,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786221634</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>47.786192</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
+          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1379,31 +1387,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1411,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786220197</t>
+          <t>1786227616</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>48.498994</t>
+          <t>4.833333</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,23 +1483,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
+          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786220102</t>
+          <t>1786221634</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
+          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.95088</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
+          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786215586</t>
+          <t>1786220197</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.540878</t>
+          <t>48.498994</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,28 +1699,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
+          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.18362</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1731,27 +1731,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786215460</t>
+          <t>1786220102</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>23.179991</t>
+          <t>138.88</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1818,22 +1818,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1843,27 +1843,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786215452</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>11.209581</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,39 +1915,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20.24912</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Aurora 0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1970,7 +1962,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2000,7 +1992,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.069128</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,7 +2019,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2042,7 +2034,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2112,7 +2104,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2114,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>36.862275</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,12 +2131,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2154,22 +2146,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.8877</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora 0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2179,27 +2171,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2209,7 +2201,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2224,17 +2216,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786215147</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,12 +2243,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2266,22 +2258,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2291,27 +2283,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2321,7 +2313,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2336,17 +2328,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786214770</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>43.961538</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,31 +2355,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786211480</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>8.297872</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,31 +2467,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2499,27 +2507,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2529,7 +2537,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2544,17 +2552,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2579,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2579,31 +2587,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Aurora +0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2611,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,28 +2683,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2715,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,12 +2787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora +0.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2827,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,39 +2899,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2954,7 +2946,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2984,7 +2976,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2994,7 +2986,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,31 +3003,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3130,22 +3130,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
+          <t>San Antonio Bulo Bulo -1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,7 +3227,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3235,31 +3235,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3282,7 +3274,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3322,7 +3314,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,7 +3331,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3354,22 +3346,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3394,7 +3386,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3434,7 +3426,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3451,7 +3443,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3466,22 +3458,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3506,7 +3498,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3546,7 +3538,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,7 +3555,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3578,39 +3570,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3618,7 +3610,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3658,7 +3650,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3675,7 +3667,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3690,39 +3682,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo 0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3730,7 +3722,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3745,7 +3737,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3770,7 +3762,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3787,7 +3779,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3802,22 +3794,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3842,7 +3834,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3872,7 +3864,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3882,7 +3874,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3899,7 +3891,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3914,17 +3906,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3954,7 +3946,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3969,7 +3961,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3984,7 +3976,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3994,7 +3986,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4011,7 +4003,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4019,23 +4011,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4043,27 +4043,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4123,23 +4123,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4147,27 +4155,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4192,17 +4200,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4219,23 +4227,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4296,7 +4304,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4306,7 +4314,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4323,27 +4331,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4351,26 +4355,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4443,19 +4443,15 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4463,34 +4459,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4520,7 +4512,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4530,7 +4522,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4547,31 +4539,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4579,27 +4579,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4666,22 +4666,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4691,27 +4691,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4763,28 +4763,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4795,27 +4795,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4840,17 +4840,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,31 +4867,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4914,7 +4922,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4944,7 +4952,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4954,7 +4962,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4971,7 +4979,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4982,12 +4990,12 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5003,27 +5011,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5048,17 +5056,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5075,7 +5083,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5086,12 +5094,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5107,27 +5115,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5152,17 +5160,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5179,39 +5187,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,39 +5291,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5331,27 +5323,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5376,17 +5368,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5403,12 +5395,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5418,22 +5410,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5458,7 +5450,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5488,7 +5480,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5498,7 +5490,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5515,12 +5507,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5530,22 +5522,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5570,7 +5562,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5600,7 +5592,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5610,7 +5602,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5627,7 +5619,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5642,22 +5634,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5682,7 +5674,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5712,7 +5704,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5722,7 +5714,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5739,12 +5731,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5754,22 +5746,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5779,27 +5771,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5824,17 +5816,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5851,12 +5843,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5866,22 +5858,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5906,7 +5898,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5936,7 +5928,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5946,7 +5938,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5963,23 +5955,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5987,7 +5983,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6067,31 +6067,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6114,7 +6122,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6144,7 +6152,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6154,7 +6162,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6171,7 +6179,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6182,17 +6190,17 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6203,27 +6211,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6248,17 +6256,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6275,7 +6283,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6283,46 +6291,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6387,54 +6387,46 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6442,7 +6434,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6472,7 +6464,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6482,7 +6474,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6499,23 +6491,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6523,7 +6519,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6715,7 +6715,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6726,7 +6726,7 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6819,12 +6819,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6931,39 +6931,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Real Tomayapo -1</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6971,27 +6963,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7016,17 +7008,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7043,7 +7035,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7058,7 +7050,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7128,7 +7120,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7138,7 +7130,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7155,7 +7147,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7170,22 +7162,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7195,27 +7187,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7240,17 +7232,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7267,7 +7259,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7282,22 +7274,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7307,27 +7299,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7352,17 +7344,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7379,7 +7371,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7394,22 +7386,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7419,27 +7411,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7464,17 +7456,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7491,31 +7483,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7595,7 +7595,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7610,22 +7610,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7635,27 +7635,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7680,17 +7680,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7707,39 +7707,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7747,27 +7739,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7792,17 +7784,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7819,7 +7811,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7834,12 +7826,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7849,7 +7841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7874,7 +7866,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7904,7 +7896,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7914,7 +7906,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7931,7 +7923,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7946,22 +7938,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7986,7 +7978,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8016,7 +8008,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8026,7 +8018,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8043,7 +8035,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8058,12 +8050,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8073,24 +8065,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8098,7 +8090,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8138,7 +8130,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8155,7 +8147,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8170,22 +8162,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8210,7 +8202,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8240,7 +8232,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8250,7 +8242,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8267,7 +8259,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8282,22 +8274,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8322,7 +8314,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8352,7 +8344,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8362,7 +8354,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8379,12 +8371,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8394,7 +8386,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8464,7 +8456,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8474,7 +8466,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8491,7 +8483,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8506,22 +8498,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -0.5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8546,7 +8538,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8576,7 +8568,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8586,7 +8578,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8603,12 +8595,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8618,39 +8610,39 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8658,7 +8650,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8688,7 +8680,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8698,7 +8690,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8715,31 +8707,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8819,7 +8819,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8931,7 +8931,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8942,7 +8942,7 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>2.31576</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>8.616781</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9035,12 +9035,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9050,22 +9050,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>27.21968</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9075,27 +9075,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786116497</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>37.35119</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9147,28 +9147,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>10.0374</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9179,27 +9179,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9224,17 +9224,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116493</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>37.348465</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9251,12 +9251,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9266,22 +9266,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9291,27 +9291,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9336,17 +9336,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116236</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>62.947368</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9363,110 +9363,326 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:V86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x99d108064ee486a128c0f102cc16036611e7fb652eb8c6a0f2c32f5b772f89fc</t>
+          <t>0x9eb6a555153e34baea8891171dda98b2be770b16334f112ed6e0108fcf31e873</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x3b1faf5c1f9c937e6fcae3ef58467801391c1a89415ceb56bda0f3d6b89fad5a</t>
+          <t>0x8da5da897fc82a008953066e0a67a7834dd90fd45d8d4b0767240da829bf50c9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786239678</t>
+          <t>1786252849</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.918465</t>
+          <t>3.137255</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,62 +635,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xfc58591c771627eb6a429bb634826daa1107a573e96c81b60c2a93d505d40222</t>
+          <t>0x99d108064ee486a128c0f102cc16036611e7fb652eb8c6a0f2c32f5b772f89fc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2237</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Universitario de Vinto</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Universitario de Vinto</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x09e87d20acf35e835c5573176b05437997818c183e7c5ce4737e4924e58830f6</t>
+          <t>0x3b1faf5c1f9c937e6fcae3ef58467801391c1a89415ceb56bda0f3d6b89fad5a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786239045</t>
+          <t>1786239678</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>25.519553</t>
+          <t>1.918465</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
+          <t>0xfc58591c771627eb6a429bb634826daa1107a573e96c81b60c2a93d505d40222</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,22 +754,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.2237</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
+          <t>0x09e87d20acf35e835c5573176b05437997818c183e7c5ce4737e4924e58830f6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786234428</t>
+          <t>1786239045</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>14.281124</t>
+          <t>25.519553</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +851,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
+          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32.21729</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6913</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -906,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
+          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786232638</t>
+          <t>1786234428</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>46.607291</t>
+          <t>14.281124</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
+          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -974,17 +974,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27.56875</t>
+          <t>32.21729</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6913</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786232521</t>
+          <t>1786232638</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>46.607291</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
+          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1078,17 +1078,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.79929</t>
+          <t>27.56875</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1099,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786230822</t>
+          <t>1786232521</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>47.749292</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
+          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1182,12 +1182,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>26.79929</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786230822</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>48.536913</t>
+          <t>47.749292</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
+          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1286,12 +1286,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>47.786192</t>
+          <t>48.536913</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
+          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1390,17 +1390,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786227616</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>4.833333</t>
+          <t>47.786192</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,28 +1483,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
+          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1515,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786221634</t>
+          <t>1786227616</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>4.833333</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,39 +1587,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
+          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1627,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786220197</t>
+          <t>1786221634</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>48.498994</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,7 +1691,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
+          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1707,23 +1699,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1731,27 +1731,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786220102</t>
+          <t>1786220197</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>48.498994</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
+          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1811,31 +1811,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.95088</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1858,7 +1850,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786215586</t>
+          <t>1786220102</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>48.540878</t>
+          <t>138.88</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,31 +1907,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13.18362</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1947,27 +1947,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1992,17 +1992,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786215460</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>23.179991</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,54 +2019,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Aurora vs Club Bolivar</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Aurora vs Club Bolivar</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Club Bolivar</t>
@@ -2074,7 +2066,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2104,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786215452</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2114,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>11.209581</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,7 +2123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2146,12 +2138,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.24912</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2161,7 +2153,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aurora 0</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2186,7 +2178,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2216,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.069128</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,7 +2235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2258,12 +2250,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2273,24 +2265,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Aurora 0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Aurora vs Club Bolivar</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>Aurora</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Aurora vs Club Bolivar</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Club Bolivar</t>
@@ -2298,7 +2290,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2338,7 +2330,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36.862275</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,12 +2347,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2370,22 +2362,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11.8877</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2395,27 +2387,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2425,7 +2417,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2440,17 +2432,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786215147</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,12 +2459,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2482,12 +2474,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2552,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786214770</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>43.961538</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,31 +2571,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786211480</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>8.297872</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,28 +2683,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2715,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,27 +2787,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2815,11 +2811,7 @@
           <t>Asian Handicap (0.5)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Aurora +0.5</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2872,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,31 +2891,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Aurora +0.5</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2931,27 +2931,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2976,17 +2976,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3011,46 +3011,38 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3058,7 +3050,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3088,7 +3080,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3098,7 +3090,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,12 +3107,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3130,22 +3122,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -1</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3170,7 +3162,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3200,7 +3192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3210,7 +3202,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,7 +3219,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3235,23 +3227,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo -1</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,7 +3331,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3339,31 +3339,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3386,7 +3378,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3426,7 +3418,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,7 +3435,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3458,7 +3450,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3538,7 +3530,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,7 +3547,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3570,22 +3562,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3610,7 +3602,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3650,7 +3642,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,7 +3659,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3682,22 +3674,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>San Antonio Bulo Bulo +0.5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3722,7 +3714,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3762,7 +3754,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3779,7 +3771,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3794,12 +3786,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3809,24 +3801,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo 0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3834,7 +3826,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3874,7 +3866,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3891,7 +3883,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3906,17 +3898,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3946,7 +3938,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3961,7 +3953,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3986,7 +3978,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4003,7 +3995,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4018,22 +4010,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4058,7 +4050,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4073,7 +4065,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4088,7 +4080,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4098,7 +4090,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4115,7 +4107,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4130,39 +4122,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -4170,7 +4162,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4200,7 +4192,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4210,7 +4202,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4227,7 +4219,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4235,23 +4227,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4259,27 +4259,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4331,7 +4331,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4342,12 +4342,12 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4435,23 +4435,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4539,27 +4539,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4567,26 +4563,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
@@ -4624,7 +4616,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4634,7 +4626,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4651,12 +4643,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4666,12 +4658,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4681,32 +4673,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>Independiente Petrolero</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4736,7 +4728,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4746,7 +4738,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4763,31 +4755,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4795,27 +4795,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4840,17 +4840,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,7 +4867,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4875,31 +4875,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4922,7 +4914,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4952,7 +4944,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4962,7 +4954,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4979,31 +4971,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5011,27 +5011,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5094,12 +5094,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5115,27 +5115,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5160,17 +5160,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5187,7 +5187,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5198,7 +5198,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5302,12 +5302,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5323,27 +5323,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5368,17 +5368,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5395,39 +5395,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5435,27 +5427,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5480,17 +5472,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5507,7 +5499,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5522,12 +5514,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5592,7 +5584,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5602,7 +5594,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5619,12 +5611,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5634,22 +5626,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5674,7 +5666,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5704,7 +5696,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5714,7 +5706,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5731,7 +5723,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5746,22 +5738,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5786,7 +5778,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5826,7 +5818,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5843,7 +5835,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5858,22 +5850,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5898,7 +5890,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5928,7 +5920,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5938,7 +5930,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5955,12 +5947,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5970,22 +5962,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5995,27 +5987,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6040,17 +6032,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6067,12 +6059,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6082,22 +6074,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6107,27 +6099,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6152,17 +6144,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6179,31 +6171,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6211,27 +6211,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6256,17 +6256,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6283,7 +6283,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6294,17 +6294,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6315,27 +6315,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6360,17 +6360,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6387,7 +6387,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6398,12 +6398,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6499,46 +6499,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6546,7 +6538,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6576,7 +6568,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6586,7 +6578,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6603,12 +6595,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6618,12 +6610,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6688,7 +6680,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6698,7 +6690,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6715,7 +6707,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6723,15 +6715,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6739,7 +6735,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6819,7 +6819,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6827,19 +6827,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6847,26 +6843,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6904,7 +6896,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6914,7 +6906,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6931,7 +6923,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6939,15 +6931,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6955,7 +6951,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7035,27 +7035,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7063,26 +7059,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7120,7 +7112,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7130,7 +7122,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7147,7 +7139,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7162,22 +7154,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7187,27 +7179,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7232,17 +7224,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7259,7 +7251,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7274,22 +7266,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7299,27 +7291,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7344,17 +7336,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7371,7 +7363,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7386,7 +7378,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7456,7 +7448,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7466,7 +7458,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7483,7 +7475,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7498,22 +7490,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7523,27 +7515,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7568,17 +7560,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7595,7 +7587,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7610,12 +7602,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7680,7 +7672,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7690,7 +7682,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7707,31 +7699,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7811,39 +7811,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7851,27 +7843,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7896,17 +7888,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7923,7 +7915,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7938,12 +7930,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8008,7 +8000,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8018,7 +8010,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8035,7 +8027,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8050,12 +8042,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8065,7 +8057,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8090,7 +8082,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8120,7 +8112,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8130,7 +8122,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8147,7 +8139,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8162,22 +8154,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano 0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8202,7 +8194,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8242,7 +8234,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8259,7 +8251,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8274,39 +8266,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8314,7 +8306,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8354,7 +8346,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8371,7 +8363,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8386,22 +8378,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8426,7 +8418,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8456,7 +8448,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8466,7 +8458,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8483,7 +8475,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8498,22 +8490,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano -1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8538,7 +8530,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8578,7 +8570,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8595,12 +8587,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8610,22 +8602,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -0.5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8650,7 +8642,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8680,7 +8672,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8690,7 +8682,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8707,12 +8699,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8722,12 +8714,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8792,7 +8784,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8802,7 +8794,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8819,12 +8811,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8834,39 +8826,39 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8874,7 +8866,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8904,7 +8896,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8914,7 +8906,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8931,7 +8923,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8939,15 +8931,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8955,7 +8951,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9035,7 +9035,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9043,19 +9043,15 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>2.31576</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9063,26 +9059,22 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -9120,7 +9112,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9130,7 +9122,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>8.616781</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9147,7 +9139,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9155,15 +9147,19 @@
           <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>27.21968</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9171,7 +9167,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786116497</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>37.35119</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9251,39 +9251,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>10.0374</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Real Oruro</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9291,27 +9283,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9336,17 +9328,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786116493</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>37.348465</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9363,7 +9355,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9371,15 +9363,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9387,7 +9383,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116236</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>62.947368</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9467,39 +9467,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9507,27 +9499,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9552,17 +9544,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116231</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>79.82266</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9579,110 +9571,222 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="T86" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="V86" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V86"/>
+  <dimension ref="A1:V88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9eb6a555153e34baea8891171dda98b2be770b16334f112ed6e0108fcf31e873</t>
+          <t>0x3f87e7339ce7641747e232255f2042868382062c30ed93b0b7a7ca0f36ee1a70</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel San Jose vs Always Ready</t>
+          <t>Club Real Potosí vs Blooming</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel San Jose</t>
+          <t>Club Real Potosí</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x8da5da897fc82a008953066e0a67a7834dd90fd45d8d4b0767240da829bf50c9</t>
+          <t>0xf36cbd9e0b3248eb13664b103f49b97a72f3e5fed3bd9cd317a60220ee91e4ce</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19701305</t>
+          <t>L19702530</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786252849</t>
+          <t>1786270216</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786310100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.137255</t>
+          <t>21.680217</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x99d108064ee486a128c0f102cc16036611e7fb652eb8c6a0f2c32f5b772f89fc</t>
+          <t>0xb707f963d108b439adff58d7c5d9c76c15a02e9e14c9a6a7eb72189c3d6341cd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Club Real Potosí vs Blooming</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Club Real Potosí</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x3b1faf5c1f9c937e6fcae3ef58467801391c1a89415ceb56bda0f3d6b89fad5a</t>
+          <t>0xf36cbd9e0b3248eb13664b103f49b97a72f3e5fed3bd9cd317a60220ee91e4ce</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19702530</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786239678</t>
+          <t>1786267150</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786310100</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.918465</t>
+          <t>66.487395</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xfc58591c771627eb6a429bb634826daa1107a573e96c81b60c2a93d505d40222</t>
+          <t>0x9eb6a555153e34baea8891171dda98b2be770b16334f112ed6e0108fcf31e873</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,31 +747,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2237</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Universitario de Vinto</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -779,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x09e87d20acf35e835c5573176b05437997818c183e7c5ce4737e4924e58830f6</t>
+          <t>0x8da5da897fc82a008953066e0a67a7834dd90fd45d8d4b0767240da829bf50c9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786239045</t>
+          <t>1786252849</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>25.519553</t>
+          <t>3.137255</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,39 +843,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
+          <t>0x99d108064ee486a128c0f102cc16036611e7fb652eb8c6a0f2c32f5b772f89fc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -906,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
+          <t>0x3b1faf5c1f9c937e6fcae3ef58467801391c1a89415ceb56bda0f3d6b89fad5a</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786234428</t>
+          <t>1786239678</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>14.281124</t>
+          <t>1.918465</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
+          <t>0xfc58591c771627eb6a429bb634826daa1107a573e96c81b60c2a93d505d40222</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -971,23 +955,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.21729</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6913</t>
+          <t>1.2237</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1010,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
+          <t>0x09e87d20acf35e835c5573176b05437997818c183e7c5ce4737e4924e58830f6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786232638</t>
+          <t>1786239045</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>46.607291</t>
+          <t>25.519553</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,31 +1059,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
+          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27.56875</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
+          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786232521</t>
+          <t>1786234428</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>14.281124</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
+          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1182,17 +1182,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.79929</t>
+          <t>32.21729</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.6913</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1203,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786230822</t>
+          <t>1786232638</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>47.749292</t>
+          <t>46.607291</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
+          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1286,17 +1286,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>27.56875</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786232521</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>48.536913</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
+          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1390,7 +1390,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>26.79929</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786230822</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>47.786192</t>
+          <t>47.749292</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
+          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1494,17 +1494,17 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786227616</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>4.833333</t>
+          <t>48.536913</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,28 +1587,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
+          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1619,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786221634</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>47.786192</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,7 +1691,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
+          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1699,31 +1699,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1731,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1776,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786220197</t>
+          <t>1786227616</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>48.498994</t>
+          <t>4.833333</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,23 +1795,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
+          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1880,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786220102</t>
+          <t>1786221634</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1890,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,7 +1899,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
+          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1922,22 +1914,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.95088</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1947,27 +1939,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
+          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1992,17 +1984,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786215586</t>
+          <t>1786220197</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.540878</t>
+          <t>48.498994</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,28 +2011,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
+          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.18362</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2051,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2096,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786215460</t>
+          <t>1786220102</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>23.179991</t>
+          <t>138.88</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,7 +2115,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2138,22 +2130,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2163,27 +2155,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2200,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786215452</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>11.209581</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,39 +2227,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20.24912</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Aurora 0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2290,7 +2274,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2320,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>48.069128</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,7 +2331,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2362,7 +2346,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2432,7 +2416,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2442,7 +2426,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36.862275</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,12 +2443,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2474,22 +2458,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>11.8877</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora 0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2499,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2529,7 +2513,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2544,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786215147</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,12 +2555,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2586,22 +2570,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2611,27 +2595,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2641,7 +2625,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2656,17 +2640,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786214770</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>43.961538</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,31 +2667,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2730,7 +2722,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2745,7 +2737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2760,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786211480</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2770,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>8.297872</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,31 +2779,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2819,27 +2819,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,7 +2891,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,31 +2899,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Aurora +0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2931,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2976,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,28 +2995,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3035,27 +3027,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3072,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,12 +3099,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3122,22 +3114,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora +0.5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3147,27 +3139,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3184,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,39 +3211,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3274,7 +3258,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3304,7 +3288,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3314,7 +3298,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,31 +3315,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3378,7 +3370,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3408,7 +3400,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3418,7 +3410,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,7 +3427,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3450,22 +3442,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
+          <t>San Antonio Bulo Bulo -1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3490,7 +3482,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3520,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3530,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,7 +3539,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3555,31 +3547,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3602,7 +3586,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3642,7 +3626,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,7 +3643,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3674,22 +3658,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3714,7 +3698,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3754,7 +3738,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,7 +3755,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3786,22 +3770,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3826,7 +3810,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3866,7 +3850,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,7 +3867,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3898,39 +3882,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -3938,7 +3922,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3978,7 +3962,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3995,7 +3979,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4010,39 +3994,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>San Antonio Bulo Bulo 0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -4050,7 +4034,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4065,7 +4049,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4090,7 +4074,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4107,7 +4091,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4122,22 +4106,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4162,7 +4146,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4192,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4202,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4219,7 +4203,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4234,17 +4218,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4274,7 +4258,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4289,7 +4273,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4304,7 +4288,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4314,7 +4298,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4331,7 +4315,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4339,23 +4323,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4363,27 +4355,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4408,17 +4400,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4435,7 +4427,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4443,23 +4435,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4467,27 +4467,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4539,23 +4539,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,27 +4643,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4671,26 +4667,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
@@ -4698,7 +4690,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4728,7 +4720,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4738,7 +4730,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,7 +4747,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4763,19 +4755,15 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4783,34 +4771,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>The Strongest vs Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Independiente Petrolero</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>The Strongest vs Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>The Strongest</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4840,7 +4824,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4834,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,31 +4851,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4899,27 +4891,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4944,17 +4936,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4971,12 +4963,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4986,22 +4978,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5011,27 +5003,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5056,17 +5048,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5083,28 +5075,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5115,27 +5107,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5160,17 +5152,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5187,31 +5179,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5302,12 +5302,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5323,27 +5323,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5368,17 +5368,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5395,7 +5395,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5406,12 +5406,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5427,27 +5427,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5472,17 +5472,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5499,39 +5499,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5554,7 +5546,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5584,7 +5576,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5594,7 +5586,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5611,39 +5603,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5651,27 +5635,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5696,17 +5680,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5723,12 +5707,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5738,22 +5722,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5778,7 +5762,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5808,7 +5792,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5818,7 +5802,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5835,12 +5819,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5850,22 +5834,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5890,7 +5874,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5920,7 +5904,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5930,7 +5914,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5947,7 +5931,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5962,22 +5946,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6002,7 +5986,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6032,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6042,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6059,12 +6043,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6074,22 +6058,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6099,27 +6083,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6144,17 +6128,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6171,12 +6155,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6186,22 +6170,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6226,7 +6210,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6256,7 +6240,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6266,7 +6250,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6283,23 +6267,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6307,7 +6295,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6360,7 +6352,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6370,7 +6362,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6387,31 +6379,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6502,17 +6502,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6523,27 +6523,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6568,17 +6568,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6595,7 +6595,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6603,46 +6603,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6650,7 +6642,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6680,7 +6672,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6690,7 +6682,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6707,54 +6699,46 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6762,7 +6746,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6792,7 +6776,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6802,7 +6786,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6819,23 +6803,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6843,7 +6831,11 @@
           <t>Division Profesional</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6896,7 +6888,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6906,7 +6898,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6923,7 +6915,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6938,7 +6930,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7008,7 +7000,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7018,7 +7010,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7035,7 +7027,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7046,7 +7038,7 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7112,7 +7104,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7122,7 +7114,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7139,12 +7131,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7154,12 +7146,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7224,7 +7216,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7234,7 +7226,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7251,39 +7243,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Real Tomayapo -1</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7291,27 +7275,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7336,17 +7320,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7363,7 +7347,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7378,7 +7362,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7448,7 +7432,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7458,7 +7442,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7475,7 +7459,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7490,22 +7474,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7515,27 +7499,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7560,17 +7544,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7587,7 +7571,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7602,22 +7586,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7627,27 +7611,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7672,17 +7656,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7699,7 +7683,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7714,22 +7698,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7739,27 +7723,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7784,17 +7768,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7811,31 +7795,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7858,7 +7850,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7888,7 +7880,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7898,7 +7890,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7915,7 +7907,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7930,22 +7922,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7955,27 +7947,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8000,17 +7992,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8027,39 +8019,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8067,27 +8051,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8112,17 +8096,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8139,7 +8123,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8154,12 +8138,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8169,7 +8153,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8194,7 +8178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8224,7 +8208,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8234,7 +8218,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8251,7 +8235,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8266,22 +8250,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8306,7 +8290,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8336,7 +8320,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8346,7 +8330,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8363,7 +8347,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8378,12 +8362,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8393,24 +8377,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8418,7 +8402,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8458,7 +8442,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8475,7 +8459,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8490,22 +8474,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>17.6089</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.3662</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8530,7 +8514,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8560,7 +8544,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8570,7 +8554,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>48.078908</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8587,7 +8571,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8602,22 +8586,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>33.06999</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.7338</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8642,7 +8626,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8672,7 +8656,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8682,7 +8666,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>45.069833</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8699,12 +8683,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8714,7 +8698,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>22.48</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8784,7 +8768,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8794,7 +8778,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>48.085561</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8811,7 +8795,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8826,22 +8810,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano -0.5</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8866,7 +8850,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8896,7 +8880,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786118874</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8906,7 +8890,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>48.067653</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8923,12 +8907,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8938,39 +8922,39 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.4675</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8978,7 +8962,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9008,7 +8992,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786117945</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9018,7 +9002,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>24.427807</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9035,31 +9019,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9082,7 +9074,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9112,7 +9104,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786116567</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9122,7 +9114,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>27.718919</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9139,7 +9131,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9154,7 +9146,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>6.27945</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9224,7 +9216,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9234,7 +9226,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>8.616741</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9251,7 +9243,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9262,7 +9254,7 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>2.31576</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -9328,7 +9320,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786116498</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9338,7 +9330,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>8.616781</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9355,12 +9347,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9370,22 +9362,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>27.21968</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7288</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9395,27 +9387,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9440,17 +9432,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786116497</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>37.35119</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9467,28 +9459,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>10.0374</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.2688</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9499,27 +9491,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9544,17 +9536,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786116493</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>37.348465</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9571,12 +9563,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9586,22 +9578,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>17.94</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.285</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9611,27 +9603,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9656,17 +9648,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786116236</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>62.947368</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9683,110 +9675,326 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T88" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="V88" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V88"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x3f87e7339ce7641747e232255f2042868382062c30ed93b0b7a7ca0f36ee1a70</t>
+          <t>0x5b322d78a31b179b483526a6a43fc5c378d37fc5ff65abdf071efa09cd314e48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,7 +539,11 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>10</t>
@@ -547,15 +551,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -0.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Club Real Potosí vs Blooming</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Club Real Potosí</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xf36cbd9e0b3248eb13664b103f49b97a72f3e5fed3bd9cd317a60220ee91e4ce</t>
+          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19702530</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786270216</t>
+          <t>1786287108</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786310100</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>21.680217</t>
+          <t>16.842105</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb707f963d108b439adff58d7c5d9c76c15a02e9e14c9a6a7eb72189c3d6341cd</t>
+          <t>0x8dc8d762598363141f470d537165df189745539e0c5fddc24c49c0afa2393abf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,12 +654,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xf36cbd9e0b3248eb13664b103f49b97a72f3e5fed3bd9cd317a60220ee91e4ce</t>
+          <t>0xd61e4e38b9905445ddc0e1fb12c6433c3f185fccfc4e98e1eea9783670c34e55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786267150</t>
+          <t>1786285499</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>66.487395</t>
+          <t>12.1212</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9eb6a555153e34baea8891171dda98b2be770b16334f112ed6e0108fcf31e873</t>
+          <t>0xe950276580c0ffc4fac05144b2a788ef5dbcc0b4c66b81ec1812a9e70de1c952</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,17 +758,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3825</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x8da5da897fc82a008953066e0a67a7834dd90fd45d8d4b0767240da829bf50c9</t>
+          <t>0x8c87043f13f58cd2cbaad9b1709261969ac1840b6c16fcb05ff62e22b74a4551</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786252849</t>
+          <t>1786280524</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.137255</t>
+          <t>6.898551</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +851,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x99d108064ee486a128c0f102cc16036611e7fb652eb8c6a0f2c32f5b772f89fc</t>
+          <t>0x5a202e680ad175e9dd461a9d27f007df345c36ca5afc88f422eb73d81f6aaedf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5212</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -875,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x3b1faf5c1f9c937e6fcae3ef58467801391c1a89415ceb56bda0f3d6b89fad5a</t>
+          <t>0x8c87043f13f58cd2cbaad9b1709261969ac1840b6c16fcb05ff62e22b74a4551</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786239678</t>
+          <t>1786280518</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.918465</t>
+          <t>5.533981</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfc58591c771627eb6a429bb634826daa1107a573e96c81b60c2a93d505d40222</t>
+          <t>0x2fdde19467ddd7f7bcd88242c99afa3a47213d3a6af3eef7b2edd79ee709159e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -955,31 +963,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2237</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Universitario de Vinto</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -987,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x09e87d20acf35e835c5573176b05437997818c183e7c5ce4737e4924e58830f6</t>
+          <t>0xc2aaa0bc4cdd8c52312166fa14665895336410353dab9ead6ef30fe0ed385a12</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786239045</t>
+          <t>1786280515</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>25.519553</t>
+          <t>30.626866</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,39 +1059,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
+          <t>0xc6abe335fd1ea50e1d90afe62844573e69aa57906c68cad9a7c91b96ea5d4726</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.35959</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1099,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
+          <t>0x8c87043f13f58cd2cbaad9b1709261969ac1840b6c16fcb05ff62e22b74a4551</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786234428</t>
+          <t>1786280514</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>14.281124</t>
+          <t>0.698233</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
+          <t>0x6422c0a05bb4938afc4f185db37bab1c9e747e118d742e92f980e05fc4f54b35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1182,17 +1174,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.21729</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6913</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1203,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
+          <t>0xc2aaa0bc4cdd8c52312166fa14665895336410353dab9ead6ef30fe0ed385a12</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786232638</t>
+          <t>1786280405</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>46.607291</t>
+          <t>29.520295</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,31 +1267,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
+          <t>0x9e9a39f92f05b654488d2424b78b7e837d345ee590e5f5614abff262df236deb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27.56875</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -0.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
+          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786232521</t>
+          <t>1786278655</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>1.582979</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,31 +1379,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
+          <t>0x2aaf2bbf5cf53e45af63e480d3e2216ba611282b20160fe36af961db805982c7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26.79929</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -1</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1411,27 +1419,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0xc0196d42938baf291922731a74fd66077f7bfe685c5af59ed2398d914b1cd00c</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1464,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786230822</t>
+          <t>1786278655</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>47.749292</t>
+          <t>1.582979</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,7 +1491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
+          <t>0xeeebf158942e22af451ec240686f86781e2019b015aab8d9182bfffcaae6cb1c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1491,23 +1499,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -0.5</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1515,27 +1531,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,17 +1576,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786278182</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>48.536913</t>
+          <t>16.949153</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
+          <t>0x22108c347bd2eed82e726fd66a4e5af989512d3b1cc616a723000e23def5b155</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1595,23 +1611,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -1.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1619,27 +1643,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,17 +1688,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786230821</t>
+          <t>1786278178</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>47.786192</t>
+          <t>2.721088</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,31 +1715,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
+          <t>0x0cd645b0a00e2cfb628e3de9be49dd41ca8da2c84af2253aee79fc9af9d6fd7f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>12.07986</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -1</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1723,27 +1755,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0xc0196d42938baf291922731a74fd66077f7bfe685c5af59ed2398d914b1cd00c</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1768,17 +1800,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786227616</t>
+          <t>1786278178</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4.833333</t>
+          <t>25.565841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,31 +1827,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
+          <t>0x7f739086dd3425f6716708590c78fc172b777644cd71e1cbd277385a8026bed6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -1</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1827,27 +1867,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0xc0196d42938baf291922731a74fd66077f7bfe685c5af59ed2398d914b1cd00c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1872,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786221634</t>
+          <t>1786278177</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13.888889</t>
+          <t>21.164021</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
+          <t>0x3f87e7339ce7641747e232255f2042868382062c30ed93b0b7a7ca0f36ee1a70</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1907,31 +1947,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1939,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>Club Real Potosí vs Blooming</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Club Real Potosí</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
+          <t>0xf36cbd9e0b3248eb13664b103f49b97a72f3e5fed3bd9cd317a60220ee91e4ce</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19702530</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786220197</t>
+          <t>1786270216</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786310100</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>48.498994</t>
+          <t>21.680217</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
+          <t>0xb707f963d108b439adff58d7c5d9c76c15a02e9e14c9a6a7eb72189c3d6341cd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2022,17 +2054,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.0625</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2043,27 +2075,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Club Real Potosí vs Blooming</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Club Real Potosí</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
+          <t>0xf36cbd9e0b3248eb13664b103f49b97a72f3e5fed3bd9cd317a60220ee91e4ce</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19702530</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,17 +2120,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786220102</t>
+          <t>1786267150</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786310100</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>138.88</t>
+          <t>66.487395</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
+          <t>0x9eb6a555153e34baea8891171dda98b2be770b16334f112ed6e0108fcf31e873</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2123,31 +2155,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.95088</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.3825</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2155,27 +2179,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
+          <t>0x8da5da897fc82a008953066e0a67a7834dd90fd45d8d4b0767240da829bf50c9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2200,17 +2224,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786215586</t>
+          <t>1786252849</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>48.540878</t>
+          <t>3.137255</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,28 +2251,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
+          <t>0x99d108064ee486a128c0f102cc16036611e7fb652eb8c6a0f2c32f5b772f89fc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13.18362</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.5212</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2259,27 +2283,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
+          <t>0x3b1faf5c1f9c937e6fcae3ef58467801391c1a89415ceb56bda0f3d6b89fad5a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2304,17 +2328,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786215460</t>
+          <t>1786239678</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>23.179991</t>
+          <t>1.918465</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,7 +2355,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
+          <t>0xfc58591c771627eb6a429bb634826daa1107a573e96c81b60c2a93d505d40222</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2346,22 +2370,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.2237</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2371,27 +2395,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x09e87d20acf35e835c5573176b05437997818c183e7c5ce4737e4924e58830f6</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,17 +2440,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786215452</t>
+          <t>1786239045</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>11.209581</t>
+          <t>25.519553</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,12 +2467,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
+          <t>0x049c7a5efc41d5f6215b141b0f1ba7291e693ca9c8b4f9b41be43bcc345ca8c6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2458,22 +2482,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.24912</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Aurora 0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2483,27 +2507,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
+          <t>0x4b9a41ca698cc29355cef1bcf7a22ee92fe3752d52092b0245d7b44f6dbb0ee8</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2528,17 +2552,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786234428</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>48.069128</t>
+          <t>14.281124</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,7 +2579,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
+          <t>0x2217dfd59e6b3229ddacc5c5603ee714a565f97766eb371d9037e4e1095b6e65</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2563,31 +2587,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>32.21729</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.6913</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2595,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Aurora vs Club Bolivar</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Club Bolivar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19697404</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2640,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786215451</t>
+          <t>1786232638</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786231800</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>36.862275</t>
+          <t>46.607291</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,27 +2683,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
+          <t>0x8bf874e3d6ff27f57bca30d6c1e8be2de990cf9dcbb5b425f5b2e2a2a89170c0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.8877</t>
+          <t>27.56875</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2695,11 +2707,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2707,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0x027635275007e9f113790e300c7aaedd02b1b3963a318f1dc80d3855211f9ae7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2737,7 +2745,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2752,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786215147</t>
+          <t>1786232521</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,39 +2787,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
+          <t>0x2830791438dbf28141148e9239f6833c58eb345899f68da797447ad01de5cb48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>26.79929</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -2819,27 +2819,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786214770</t>
+          <t>1786230822</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>43.961538</t>
+          <t>47.749292</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,7 +2891,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
+          <t>0xb49d50fd422bbd24fe387314d68a1042a66f62aff0473f3bda9edccf743bc14e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2902,17 +2902,17 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2923,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786211480</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>8.297872</t>
+          <t>48.536913</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,28 +2995,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
+          <t>0xb16966432c294729a654e0cc6243c77d373fa7ec3dd3a37c76d2ea47221ed347</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4537</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786197551</t>
+          <t>1786230821</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2.203857</t>
+          <t>47.786192</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
+          <t>0xb68c1d242f46686efe088314e66b4f493f52072cdb2ce3acd22b6b9bdde86771</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3107,19 +3107,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3127,11 +3123,7 @@
           <t>Asian Handicap (0.5)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Aurora +0.5</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3184,7 +3176,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786196281</t>
+          <t>1786227616</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3186,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>23.689655</t>
+          <t>4.833333</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,28 +3203,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
+          <t>0x94a4af51480b2c67ca5d1b6184264756d23a7e06afae0c2ae53909fa3a6627ff</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>32.91998</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3258,7 +3250,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3288,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786195183</t>
+          <t>1786221634</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>46.04193</t>
+          <t>13.888889</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,12 +3307,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
+          <t>0x2de5f95199e6c91289462c277458b9285c4769eee3e97d6bb4d264e6ca3cd91f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3330,22 +3322,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29.37697</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3355,27 +3347,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x6fb3760eea1cb799154ce68d64979cc5e0fc5b96984a1188ed89361c6685a9a0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3400,17 +3392,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786195177</t>
+          <t>1786220197</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>48.556975</t>
+          <t>48.498994</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,7 +3419,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
+          <t>0x945db2815c8e3a02ba323b4a4f1c2bd6f19ee94d3dea19a0b3905dc488f00f7d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3435,31 +3427,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.0625</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3482,7 +3466,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
+          <t>0xce43282ec1c1653090b7bf0f38a745f9b0696058731cf714bde0eac6147796b4</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3512,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786195106</t>
+          <t>1786220102</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>21.275862</t>
+          <t>138.88</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,7 +3523,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
+          <t>0x78437da72cb04965b0256e7646a9e96444b108bc1fab682a8a027b4d8967ea92</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3547,23 +3531,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>60.35625</t>
+          <t>9.95088</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3586,7 +3578,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x938a88c643a3712f3dc6518a1b3d9a80ef55ee685b77425cd815340bd7bbd770</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3616,7 +3608,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786215586</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3618,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>48.540878</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,39 +3635,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
+          <t>0x96465eb3344e674ab2841a36c47e005c10d64a941c99a71b136787d4b265684e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>13.18362</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -3683,27 +3667,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0x4bfa75dea2b6169338568759ddfb3dba041c798a19e7fb18e964a1284b89dde4</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3728,17 +3712,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786215460</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>31.308357</t>
+          <t>23.179991</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,7 +3739,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
+          <t>0x5833eb8e5cd34798d3bfca6d02cfb639998d8e504e10809fb7ed1a889be0587b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3770,22 +3754,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6.87233</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4338</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo -0.5</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3795,27 +3779,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3840,17 +3824,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786215452</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>15.843988</t>
+          <t>11.209581</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,7 +3851,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
+          <t>0x90f5b0efc71bedddc79202fd5c7b0ba4e625005448f40f9d77aba9e0c935acc6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3882,22 +3866,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>33.34531</t>
+          <t>20.24912</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.6938</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
+          <t>Aurora 0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3907,27 +3891,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0x9d9258806c692e5f1bc4e64ef4a9592cd7bb8c730538cc1bcb4fae28922410d0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,17 +3936,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>48.065312</t>
+          <t>48.069128</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,7 +3963,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
+          <t>0x5e53d68f84419f1e446bba3c3784a2416ec9b1266ca237f96e4a2e06aee4adb7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3994,12 +3978,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>27.58646</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4009,7 +3993,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo 0</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4019,27 +4003,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
+          <t>0xd15df5efe1db657226029089be113cdd85422f2b285d258b1707fce688ad4966</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4064,17 +4048,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786215451</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>47.976452</t>
+          <t>36.862275</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4091,12 +4075,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
+          <t>0xa86e8e5c083cdaf773dd76a0cfdeaf7eadaeb7e3a2912300688e6f4856b98abe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4106,39 +4090,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.00352</t>
+          <t>11.8877</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -4146,7 +4130,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4161,7 +4145,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4176,7 +4160,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786215147</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4186,7 +4170,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.00577</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,12 +4187,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
+          <t>0xd61f1cc51ee57233d061e4865203fa79de21319afc00edb1d4f58bcd9e6ea20d</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4218,12 +4202,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>38.38875</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4233,24 +4217,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Nacional Potosí</t>
@@ -4258,7 +4242,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
+          <t>0xb3088daebe9cea6aa0766f6f96dec2561b1e37e446bfe040b18718973db59727</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4288,7 +4272,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786195105</t>
+          <t>1786214770</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4298,7 +4282,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>43.961538</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,7 +4299,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
+          <t>0xaab0cfe3b9cf7d91b62dbb8f96b295abcbd1b552b3f2b41499b4060d2023fa78</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4323,31 +4307,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo +0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4370,7 +4346,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
+          <t>0xd04ed259810985afccb1cfc85f071bdbc6aef17bedf20fd6144f1696f7f096d3</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4400,7 +4376,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786195103</t>
+          <t>1786211480</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4410,7 +4386,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>47.478261</t>
+          <t>8.297872</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4427,39 +4403,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
+          <t>0xb3f688560e5fa99309304c9b24d3cd6415d9db6f10176fe6fc7fba325ddbecdb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x204e31304364d2A5f7B90dE28F507adc449Ae221</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.4537</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4467,27 +4435,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4512,17 +4480,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786194848</t>
+          <t>1786197551</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>4.857143</t>
+          <t>2.203857</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4539,7 +4507,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
+          <t>0xd9a386b5b31c5e80c3fee90814e3407c3e00267793e1b9831d920bdaf2c81b50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4547,23 +4515,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Aurora +0.5</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4571,27 +4547,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>Aurora vs Club Bolivar</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Club Bolivar</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x6b5de8e452e82fa8148617665da1413ab803746f54de4d392386667d7c45216b</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19697404</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4616,17 +4592,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786189746</t>
+          <t>1786196281</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786231800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>50.421622</t>
+          <t>23.689655</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,23 +4619,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
+          <t>0x3a38637745d90bd7102527c4781bb072ab02e99cafd8798865aa0a7e1bf3db6d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.76989</t>
+          <t>32.91998</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>1.715</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4675,27 +4651,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4720,17 +4696,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786187481</t>
+          <t>1786195183</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.89293</t>
+          <t>46.04193</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4747,7 +4723,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
+          <t>0x55122ed68065e4751f17214e32fee3a429abbf81a3253b8dde8f08973fe72723</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4755,23 +4731,31 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>21.125</t>
+          <t>29.37697</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -4779,27 +4763,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4824,17 +4808,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786182543</t>
+          <t>1786195177</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>48.556975</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4851,12 +4835,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
+          <t>0x46f6d0a096071f9553caf9887c38be43a8c38994c8fecb94b9c471fba9d6407d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4866,22 +4850,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.00999</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.8275</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo -1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4891,27 +4875,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
+          <t>0x572c2e0964829391092b353aaaa78e7e28b060171bc9db036b211dfe9933a13f</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4936,17 +4920,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786178250</t>
+          <t>1786195106</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.220532</t>
+          <t>21.275862</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4963,27 +4947,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
+          <t>0xfed19fe86b3e3e632ca830585606613e7a93ae6ad5117360b9dad5173a216c8c</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>60.35625</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4991,11 +4971,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5003,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>The Strongest vs Independiente Petrolero</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19692641</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5048,17 +5024,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786173034</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786223700</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>272.275862</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5075,31 +5051,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
+          <t>0xfd1cbabae1b405cb08b74afbe336b282074f40fe481ef67a40e0be5cc9ae7931</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5837</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo -0.5</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5107,27 +5091,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5152,17 +5136,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786136236</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>19.374732</t>
+          <t>31.308357</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5179,12 +5163,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
+          <t>0xd42dd327b03d2ea530e7167c14a5168fbe2e10b98825a1a094c405aa766c0e9e</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5194,22 +5178,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>6.87233</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5525</t>
+          <t>1.4338</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>San Antonio Bulo Bulo -0.5</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5219,27 +5203,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0x2c0ec79dec2ab53ddb8a5287ec7d95bf971677a0e028e5a731f7a54e7c0abe52</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5264,17 +5248,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786136032</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>60.307692</t>
+          <t>15.843988</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5291,7 +5275,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
+          <t>0x9b8b2842dd0951d3c4366f7060d328ca1e61449f83c3e64e7d0914def43150e9</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5299,23 +5283,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>33.34531</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.6938</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo +0.5</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5323,27 +5315,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5368,17 +5360,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786135821</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13.395349</t>
+          <t>48.065312</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5395,7 +5387,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
+          <t>0x701d48c5010cd94db117950f79e8eaaa4046224d4d26a717aa8d7c61e5095603</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5403,23 +5395,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>27.58646</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.575</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo 0</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5427,27 +5427,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x64e8fbde06d75afcc700321671be111bc82be43393253e5ea31d0c636db8d25d</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5472,17 +5472,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786135233</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>8.961131</t>
+          <t>47.976452</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
+          <t>0x67f75c5c065a0c47fe8cd4aa720ccb550723e38e68fb0686ce31509462b59aff</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5507,23 +5507,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17.00737</t>
+          <t>0.00352</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5531,27 +5539,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5576,17 +5584,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786134933</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>48.077371</t>
+          <t>0.00577</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5603,7 +5611,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
+          <t>0x2e58a9ca7120775a2375e8a262fd0a43fc945a44467f89303c8b8f90dcd1bc54</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5611,23 +5619,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>38.38875</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5635,27 +5651,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
+          <t>0x081bb51d955089c34fdb4b68edb7865f2b634b7c6f0ee811127606474c3b71de</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5665,7 +5681,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5680,17 +5696,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786134605</t>
+          <t>1786195105</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>5.431193</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,12 +5723,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
+          <t>0x63575ab4d2736e4a56ee59ef42d1608a29914ed76390224d347e9adde4ece1ff</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5722,22 +5738,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5362</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>San Antonio Bulo Bulo +0.5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5747,27 +5763,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x08a8562230824b55509e71d718f2e97cef288c32dda0e9bec1c385176152deaa</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5792,17 +5808,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786134304</t>
+          <t>1786195103</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>9.323991</t>
+          <t>47.478261</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,12 +5835,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
+          <t>0xd9fe6ff9a73af1b39126508c958f668fae68f83d02dc70c1c0d3edee7bac0698</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5834,22 +5850,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5859,27 +5875,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x769eea56a43c49d9cf5e5fab2b3a9b72964ede8009736e9b6700553ad94c4b1c</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5904,17 +5920,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786134118</t>
+          <t>1786194848</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>49.767221</t>
+          <t>4.857143</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,7 +5947,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
+          <t>0xf39343d92792a4f591dfeab72647abe656b994a66927bfb38db6f88c28d9259b</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5939,31 +5955,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15.16819</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -5971,27 +5979,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6016,17 +6024,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786189746</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>48.538208</t>
+          <t>50.421622</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,7 +6051,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
+          <t>0xaa73d02b6f6462028f4aaf2a1f2453c2457b7b1fcb67bda7fc70f3a8fa759652</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6051,31 +6059,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18.5095</t>
+          <t>1.76989</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3813</t>
+          <t>1.935</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6083,27 +6083,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6128,17 +6128,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786131200</t>
+          <t>1786187481</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>48.549508</t>
+          <t>1.89293</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6155,39 +6155,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
+          <t>0xa3e049b9059bc91013a03aaa8ab9db007b42c2067a464c3861cb1b7ceb2f4518</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>21.125</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6195,27 +6187,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6240,17 +6232,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786131081</t>
+          <t>1786182543</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>24.373541</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6267,12 +6259,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
+          <t>0xe16eaff028990451968364aee83ca802c99521a40479400e0f271fcf1e623b4e</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6282,12 +6274,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.00999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.8275</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6297,7 +6289,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6307,27 +6299,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0xb477e72b9ab6557e336768e8602ef1b40d5140beda07a5f9765228ca871d791f</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6352,17 +6344,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786130177</t>
+          <t>1786178250</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2.605863</t>
+          <t>1.220532</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6379,12 +6371,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
+          <t>0x778d5391d91c2202456bb2794070959085f92b254fb5e58d41ebde9406162bcb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6394,22 +6386,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5088</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6419,27 +6411,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>The Strongest vs Independiente Petrolero</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
+          <t>0x614c32809a7d6ad12c22c0256c9112ab22a296220275a1694649c55e7279b319</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19692641</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6464,17 +6456,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786129447</t>
+          <t>1786173034</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786223700</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>9.82799</t>
+          <t>272.275862</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6491,28 +6483,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
+          <t>0x665ad5dc09f910a78682d8cac57b8941da70edf35f23f2fb6db3f128b63a18e8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7.35999</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.5837</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6523,27 +6515,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19691489</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6568,17 +6560,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786129377</t>
+          <t>1786136236</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786215600</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>9.945932</t>
+          <t>19.374732</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6595,31 +6587,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
+          <t>0xf272c06e82de6d4f5a541673d36a6677e813d924b288c8fa65932e7f17a6e89f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5525</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786127516</t>
+          <t>1786136032</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>7.111111</t>
+          <t>60.307692</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6699,7 +6699,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
+          <t>0x0a6830dca2ddaafc8a77ba73c5db8e87d8f5fbc96d7d4d1fc85c80dd6a2dcff0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6710,17 +6710,17 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5.75999</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6731,27 +6731,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6776,17 +6776,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786127077</t>
+          <t>1786135821</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>7.100142</t>
+          <t>13.395349</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6803,7 +6803,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
+          <t>0x1b16769a2446e95c5c45c0a5c1eee6a448ebe2fc2e9b698f501443da0dfe730a</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6811,46 +6811,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6858,7 +6850,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6888,7 +6880,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786126518</t>
+          <t>1786135233</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6898,7 +6890,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>8.961131</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6915,54 +6907,46 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
+          <t>0x3b7d6449f4a2a7f7e958feb31d1aa3512a36d932b93cd01aba4dae26404c5131</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.36115</t>
+          <t>17.00737</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -6970,7 +6954,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7000,7 +6984,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786134933</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7010,7 +6994,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>11.204221</t>
+          <t>48.077371</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7027,28 +7011,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
+          <t>0x5b2bf2a561f9efc207b4be16204e262143fe9b1140ba536a8207f25e53ad496b</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.81507</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7059,27 +7043,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xd3779282ef9e4691761048b5151f1cb89c2b98e8b99d1ab7e6e6c64113635260</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7104,17 +7088,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786126508</t>
+          <t>1786134605</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>11.204259</t>
+          <t>5.431193</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7131,12 +7115,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
+          <t>0xcc60eac075cc4315d4dfa294b65cc4f174c2c9d458811a16d52e87b659d8ad45</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7146,39 +7130,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>27.87055</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.7462</t>
+          <t>1.5362</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7186,7 +7170,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7216,7 +7200,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786134304</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7226,7 +7210,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>37.347471</t>
+          <t>9.323991</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7243,31 +7227,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
+          <t>0xe21791ae1e8109a191bcf87ea7e050cf62a2cdf8ddab67d9bf182b3016b1b848</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9.38356</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.2512</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7290,7 +7282,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7320,7 +7312,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786126505</t>
+          <t>1786134118</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7330,7 +7322,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>37.347502</t>
+          <t>49.767221</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7347,7 +7339,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
+          <t>0xc3316b5940ad1bd194feda7f00770a34f912831f1c7deace747e91137cafd11b</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7362,39 +7354,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>15.16819</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7402,7 +7394,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x48f1daf9c9d3e68c0ec6553b26f71366417addfa8f09d543cc8f8bdd0077b612</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7432,7 +7424,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786125953</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7442,7 +7434,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>48.538208</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7459,7 +7451,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
+          <t>0x3c412198bcfc31cf640052941892a1f595f5547ec59a1414e24fbb1bfeb3ebae</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7474,22 +7466,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>18.5095</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3813</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7499,27 +7491,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x2f4dc11491614174f697fd6856dc7dfbde0374f56c9c6b93da705d898b6b9392</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7544,17 +7536,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786124724</t>
+          <t>1786131200</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>15.836735</t>
+          <t>48.549508</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7571,7 +7563,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
+          <t>0x2cb6bec7f2a474ec0b4c474043876d18add5eadb31632382e7e9f728fa247159</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7586,39 +7578,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.93998</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -7626,7 +7618,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x491ded7835f0cda7922dee91d1cbc277b69bb5da61c7be630a919284af357592</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7656,7 +7648,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786124628</t>
+          <t>1786131081</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7666,7 +7658,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2.58664</t>
+          <t>24.373541</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7683,12 +7675,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
+          <t>0x2a44ccf443a8d5632916aab67a3e7bc4147a268fe5d4978cedf712cfd7e2babf</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7698,22 +7690,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.55998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7723,27 +7715,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7768,17 +7760,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786124356</t>
+          <t>1786130177</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>4.74664</t>
+          <t>2.605863</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7795,12 +7787,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
+          <t>0x116fd7242c980c72161b884392f42af79732e449e79f3dc7d212acd8ad8d658d</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7810,22 +7802,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.3713</t>
+          <t>1.5088</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Real Tomayapo -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7835,27 +7827,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x0e1c46a583926b3308cdb91be9a4c98f1faa27ed00668e5a3022fd06f96adbfb</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7880,17 +7872,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786123837</t>
+          <t>1786129447</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>24.080808</t>
+          <t>9.82799</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7907,7 +7899,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
+          <t>0xbbe9c61e5707bbf256b5c277314eeffa098594034d2dbb2bb99c6791f780e113</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7915,31 +7907,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17.66906</t>
+          <t>7.35999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Real Tomayapo -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -7947,27 +7931,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>San Antonio Bulo Bulo vs Nacional Potosí</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
+          <t>0x911bd51e46175fe9d225b374da8c9683813fac3a6ae307652700b382561964f3</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19691489</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7992,17 +7976,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786123806</t>
+          <t>1786129377</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786215600</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>48.079075</t>
+          <t>9.945932</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8019,28 +8003,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
+          <t>0xa62f250ff2f43c3bb34525d562a9f70e050c859e38dc19adf04adae248a4e98f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>27.12529</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -8051,27 +8035,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8096,17 +8080,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786123085</t>
+          <t>1786127516</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>54.115292</t>
+          <t>7.111111</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8123,7 +8107,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
+          <t>0x0858011830e20e0cbfb1e43413cbd279d8984110bee80f2ae61ebfad9aaa0ab8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8131,46 +8115,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.75999</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -8178,7 +8154,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0x68ad1bb7e88acbf83c09926e656f505fd89df351ed43ff1e7aad919a2d0cdaae</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8208,7 +8184,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786120674</t>
+          <t>1786127077</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8218,7 +8194,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>4.727273</t>
+          <t>7.100142</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8235,7 +8211,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
+          <t>0x5011867ed5b463eaca1c24497bfc1f7d948a9bc0c26c70c9d852755682ba6eee</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8250,12 +8226,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.65998</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8320,7 +8296,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786119912</t>
+          <t>1786126518</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8330,7 +8306,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2.25082</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8347,12 +8323,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
+          <t>0xb6e0812ef93e960870c52f2f1faf333136580d28861d47fde2e61935f3860f12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8362,12 +8338,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>8.36115</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8377,7 +8353,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano 0</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8402,7 +8378,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8432,7 +8408,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8442,7 +8418,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>11.204221</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8459,39 +8435,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+          <t>0x9bd982e33d22074983f5138991b39dc45e478934065574d7b45b291bc084485e</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>17.6089</t>
+          <t>2.81507</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.3662</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -1.5</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8514,7 +8482,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8544,7 +8512,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126508</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8554,7 +8522,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>48.078908</t>
+          <t>11.204259</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8571,12 +8539,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+          <t>0xc38ae621d8fca720bddf8fcfb0463c1e1a390ff07c8c974251d96d1ae7fb7c56</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8586,12 +8554,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>33.06999</t>
+          <t>27.87055</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.7338</t>
+          <t>1.7462</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8656,7 +8624,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786118876</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8666,7 +8634,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>45.069833</t>
+          <t>37.347471</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8683,39 +8651,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+          <t>0x0368c1bb4d6609c35c97b48075e98b9d2c4222ddf6302ab88136e3741e6ce3a5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>9.38356</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.2512</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano -1</t>
-        </is>
-      </c>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -8738,7 +8698,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8768,7 +8728,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786126505</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8778,7 +8738,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>48.085561</t>
+          <t>37.347502</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8795,7 +8755,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+          <t>0x7f8f46466701fdfddd757f918f5a804848fbc67ad4bdcec366e181e3d16f1b3d</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8810,22 +8770,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>12.87</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -0.5</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8850,7 +8810,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8880,7 +8840,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786118874</t>
+          <t>1786125953</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8890,7 +8850,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>48.067653</t>
+          <t>17.16</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8907,12 +8867,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+          <t>0xa73a2931f37ee8369aa2d183c637aac54b2917f644d1011c5108ce866cbac8f8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8922,12 +8882,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8937,7 +8897,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8947,27 +8907,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8992,17 +8952,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786117945</t>
+          <t>1786124724</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>24.427807</t>
+          <t>15.836735</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9019,7 +8979,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+          <t>0x7615a3a9a5753889a9bd269dd030cc5e94939d5600ca1a6b6d0287f8bf9fc8f5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9034,22 +8994,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>1.93998</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano -1</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9074,7 +9034,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9104,7 +9064,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786116567</t>
+          <t>1786124628</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9114,7 +9074,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>27.718919</t>
+          <t>2.58664</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9131,12 +9091,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+          <t>0x4e4b1dcf666f51909f26dc3ba295c4d3aaa5538529e00c4032af14f9cffe430d</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9146,12 +9106,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.27945</t>
+          <t>3.55998</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9216,7 +9176,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786124356</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9226,7 +9186,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>8.616741</t>
+          <t>4.74664</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9243,31 +9203,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+          <t>0x862b8ed2cf92c8393495af2afc0f5837c31b91839af481202ed412f03bf8971b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.31576</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.3713</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Real Tomayapo -1</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9275,27 +9243,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9320,17 +9288,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786116498</t>
+          <t>1786123837</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>8.616781</t>
+          <t>24.080808</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9347,12 +9315,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+          <t>0x3664cb675bf0848a30ca29bb1a35549acf19d0f40c4fc6c013d8aa481af892b0</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9362,22 +9330,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>27.21968</t>
+          <t>17.66906</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.7288</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo -1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9387,27 +9355,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xb9da4c9ca0557d27b99a185a3800d8d469d1bad868c55fdb946cd65a6065a888</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9432,17 +9400,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786116497</t>
+          <t>1786123806</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>37.35119</t>
+          <t>48.079075</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9459,28 +9427,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+          <t>0x467eb043a2e00a48349804e6ea64170cacb13197d8f53b68cdba9b4fecbda5c2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10.0374</t>
+          <t>27.12529</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.2688</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Division Profesional</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9491,27 +9459,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
+          <t>Real Tomayapo vs Real Oruro</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Academia De Balompie Boliviano</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Guabira</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf8758bfa74fe88e8b3ae46990bfd7fdc85028fe092095742999df545e0a58e73</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19682540</t>
+          <t>L19683272</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9536,17 +9504,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786116493</t>
+          <t>1786123085</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1786137300</t>
+          <t>1786145400</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>37.348465</t>
+          <t>54.115292</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9563,12 +9531,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+          <t>0xfb8706347229edbfbecceb1ec967cad8f2155ba3564efd2f9b129bdf52053cdd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9578,22 +9546,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>17.94</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Division Profesional</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9603,27 +9571,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9648,17 +9616,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786116236</t>
+          <t>1786120674</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>62.947368</t>
+          <t>4.727273</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9675,31 +9643,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+          <t>0x5c61b658ed160e256a1a04509c60d05282cca9ee175f758004726d00cda9fda3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>1.65998</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -9707,27 +9683,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Real Tomayapo vs Real Oruro</t>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guabira</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19683272</t>
+          <t>L19682540</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9752,17 +9728,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786116231</t>
+          <t>1786119912</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>1786145400</t>
+          <t>1786137300</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>79.82266</t>
+          <t>2.25082</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9779,7 +9755,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+          <t>0xf5bbffb37c6e30c4b29c9b786f1d3cbc6312852512b5f5b8d7e546953f1d5d41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9794,12 +9770,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1.85998</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9809,24 +9785,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>Academia De Balompie Boliviano 0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano vs Guabira</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Academia De Balompie Boliviano</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>Guabira</t>
@@ -9834,7 +9810,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+          <t>0xf2dc7e574dbabb1bf692c4f4ee6e476cf533cc7b889ce2c4d27bf689231ae30b</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9864,7 +9840,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786115704</t>
+          <t>1786118876</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9874,7 +9850,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2.56549</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9891,110 +9867,1542 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>0x937fccf05d1a03c61c6c49ecc4f09bfa4458fe95c68d2576b5936782adbdf745</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>17.6089</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.3662</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1.5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>48.078908</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x2bdb8d570c912295736becb6fb2d2e8ac3dd6846d901ec5dec62742a8fe36302</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>33.06999</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.7338</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1786118876</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>45.069833</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0x7fae1c283411af3a5d69339f0766d48c13455376b26c65fa4f1b543f0542dc68</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>22.48</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>48.085561</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0x2f90ba886d93902d9eceebc807f893a7a79859ea55117da82a029f6e15a67ffb</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>28.42</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.5913</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -0.5</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0xb76db3bf5b6df2ca9673c137392f1227cb428d254d2b85ceaf7ff3c093456f4d</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1786118874</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>48.067653</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x74a826ebfcfd5acb3a91baef87b2df562f10cbb9bdd3b492bbdb0b00c46c9690</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>11.42</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1786117945</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>24.427807</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0xc807431dabca948a7eef7c0732e33166de0f9e9ccf237561c91240f8840da1ec</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>12.82</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.4625</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano -1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x224d1b4bc2b57cc5978d2922e84bc81203465c5fd8cbeb4422d303fd7c400f1e</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1786116567</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>27.718919</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0xa0e42ac580f9d658c876264fdfce46a01d75892392accefaecd1d3bc438d404e</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6.27945</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>8.616741</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0x09e6762fac3afbc9893a9380f32b25cbcc92464d9c11ccbcf1f5d67068ea89c7</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2.31576</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1786116498</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>8.616781</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0xd1a47102f15e31997aed9d1f25b0658b9e0366499701d5990eebc4b8bb72dd8e</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>27.21968</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.7288</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1786116497</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>37.35119</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0x75feb6c5e98d8cc369d1dbddf86b8415299f2b3736a92898e07569169c537528</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0xF544c218C0Ba0BAfD9Dd049E469097AE58B235c2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>10.0374</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.2688</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1786116493</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>37.348465</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0x232a1a673706827257f912fbf14de856ef17bdfcbab1a07ac3ada89a596e5d9f</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>17.94</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0xb3ce5682da68ef1a586a9b07396d45e2457b987b733027163106acc3835c384c</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1786116236</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>62.947368</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0x34c5fcd3f87a29f4e7bcccb0185ce177b86875bd2aca2067492a8c5c5e51f6e8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>40.51</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.5075</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x03ab73c7b230138be63e39afa73d391ca5ebdd8a3f3d3b5e399ee1cd32fa1040</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19683272</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1786116231</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1786145400</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>79.82266</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0x80cde5b15660e5fc13a5df47d634f99902cb234d188fab5ab215a1da84844d7e</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>1.85998</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.725</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano vs Guabira</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Academia De Balompie Boliviano</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Guabira</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0xcd2fd1966093a1babd5bc256363d39e156a4dde6e33bbe69c5f2fd48c0a27f3c</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19682540</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1786115704</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1786137300</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>2.56549</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>0x590b15150f41ddf420690c7cecb635a5facfe4448334123e390e09254607c190</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
         <is>
           <t>9.19</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>1.3562</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano -1.5</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Division Profesional</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Division Profesional</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano vs Guabira</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Academia De Balompie Boliviano</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>Guabira</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>0x861fbd464f94d528425eae758a57be7858924dd394418e99816cd4e1df5841dd</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>L19682540</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
         <is>
           <t>1786115704</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>1786137300</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="T101" t="inlineStr">
         <is>
           <t>25.796491</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="V101" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Division Profesional/trades.xlsx
+++ b/data/sxbet/ligas/Division Profesional/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5b322d78a31b179b483526a6a43fc5c378d37fc5ff65abdf071efa09cd314e48</t>
+          <t>0xf81b705392599be8409f9daad8c65127d1a10e1f1b66da8c9f865db6ceeaa58c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5938</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Club Real Potosí vs Blooming</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Club Real Potosí</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
+          <t>0x818ce52e562db99ec7790fe1dbabed69560a1afc84c80bc686d051baf115816a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19702530</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786287108</t>
+          <t>1786288796</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786310100</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>16.842105</t>
+          <t>1.801802</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8dc8d762598363141f470d537165df189745539e0c5fddc24c49c0afa2393abf</t>
+          <t>0x5b322d78a31b179b483526a6a43fc5c378d37fc5ff65abdf071efa09cd314e48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,23 +643,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero -0.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Club Real Potosí vs Blooming</t>
+          <t>Oriente Petrolero vs Universitario de Vinto</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Club Real Potosí</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd61e4e38b9905445ddc0e1fb12c6433c3f185fccfc4e98e1eea9783670c34e55</t>
+          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19702530</t>
+          <t>L19703502</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786285499</t>
+          <t>1786287108</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786310100</t>
+          <t>1786318200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>12.1212</t>
+          <t>16.842105</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe950276580c0ffc4fac05144b2a788ef5dbcc0b4c66b81ec1812a9e70de1c952</t>
+          <t>0x8dc8d762598363141f470d537165df189745539e0c5fddc24c49c0afa2393abf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -758,17 +758,17 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5175</t>
+          <t>1.825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel San Jose vs Always Ready</t>
+          <t>Club Real Potosí vs Blooming</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel San Jose</t>
+          <t>Club Real Potosí</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x8c87043f13f58cd2cbaad9b1709261969ac1840b6c16fcb05ff62e22b74a4551</t>
+          <t>0xd61e4e38b9905445ddc0e1fb12c6433c3f185fccfc4e98e1eea9783670c34e55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19701305</t>
+          <t>L19702530</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786280524</t>
+          <t>1786285499</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786302000</t>
+          <t>1786310100</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.898551</t>
+          <t>12.1212</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5a202e680ad175e9dd461a9d27f007df345c36ca5afc88f422eb73d81f6aaedf</t>
+          <t>0xe950276580c0ffc4fac05144b2a788ef5dbcc0b4c66b81ec1812a9e70de1c952</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,12 +862,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.5175</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786280518</t>
+          <t>1786280524</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>5.533981</t>
+          <t>6.898551</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x2fdde19467ddd7f7bcd88242c99afa3a47213d3a6af3eef7b2edd79ee709159e</t>
+          <t>0x5a202e680ad175e9dd461a9d27f007df345c36ca5afc88f422eb73d81f6aaedf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,17 +966,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc2aaa0bc4cdd8c52312166fa14665895336410353dab9ead6ef30fe0ed385a12</t>
+          <t>0x8c87043f13f58cd2cbaad9b1709261969ac1840b6c16fcb05ff62e22b74a4551</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786280515</t>
+          <t>1786280518</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>30.626866</t>
+          <t>5.533981</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xc6abe335fd1ea50e1d90afe62844573e69aa57906c68cad9a7c91b96ea5d4726</t>
+          <t>0x2fdde19467ddd7f7bcd88242c99afa3a47213d3a6af3eef7b2edd79ee709159e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,17 +1070,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.35959</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.335</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x8c87043f13f58cd2cbaad9b1709261969ac1840b6c16fcb05ff62e22b74a4551</t>
+          <t>0xc2aaa0bc4cdd8c52312166fa14665895336410353dab9ead6ef30fe0ed385a12</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786280514</t>
+          <t>1786280515</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.698233</t>
+          <t>30.626866</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x6422c0a05bb4938afc4f185db37bab1c9e747e118d742e92f980e05fc4f54b35</t>
+          <t>0xc6abe335fd1ea50e1d90afe62844573e69aa57906c68cad9a7c91b96ea5d4726</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1174,17 +1174,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.35959</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3388</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xc2aaa0bc4cdd8c52312166fa14665895336410353dab9ead6ef30fe0ed385a12</t>
+          <t>0x8c87043f13f58cd2cbaad9b1709261969ac1840b6c16fcb05ff62e22b74a4551</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786280405</t>
+          <t>1786280514</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>29.520295</t>
+          <t>0.698233</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,39 +1267,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x9e9a39f92f05b654488d2424b78b7e837d345ee590e5f5614abff262df236deb</t>
+          <t>0x6422c0a05bb4938afc4f185db37bab1c9e747e118d742e92f980e05fc4f54b35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.3388</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Division Profesional</t>
@@ -1307,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Oriente Petrolero vs Universitario de Vinto</t>
+          <t>Gualberto Villarroel San Jose vs Always Ready</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Gualberto Villarroel San Jose</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
+          <t>0xc2aaa0bc4cdd8c52312166fa14665895336410353dab9ead6ef30fe0ed385a12</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19703502</t>
+          <t>L19701305</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786278655</t>
+          <t>1786280405</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786318200</t>
+          <t>1786302000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.582979</t>
+          <t>29.520295</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1371,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x2aaf2bbf5cf53e45af63e480d3e2216ba611282b20160fe36af961db805982c7</t>
+          <t>0x9e9a39f92f05b654488d2424b78b7e837d345ee590e5f5614abff262df236deb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1404,12 +1396,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero -1</t>
+          <t>Oriente Petrolero -0.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1434,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xc0196d42938baf291922731a74fd66077f7bfe685c5af59ed2398d914b1cd00c</t>
+          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1491,12 +1483,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xeeebf158942e22af451ec240686f86781e2019b015aab8d9182bfffcaae6cb1c</t>
+          <t>0x2aaf2bbf5cf53e45af63e480d3e2216ba611282b20160fe36af961db805982c7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x23a63d3fEDf22e3D422073b7226922d61587207c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1506,22 +1498,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Oriente Petrolero -0.5</t>
+          <t>Oriente Petrolero -1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1546,7 +1538,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
+          <t>0xc0196d42938baf291922731a74fd66077f7bfe685c5af59ed2398d914b1cd00c</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1576,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786278182</t>
+          <t>1786278655</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16.949153</t>
+          <t>1.582979</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x22108c347bd2eed82e726fd66a4e5af989512d3b1cc616a723000e23def5b155</t>
+          <t>0xeeebf158942e22af451ec240686f86781e2019b015aab8d9182bfffcaae6cb1c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1618,22 +1610,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Oriente Petrolero -1.5</t>
+          <t>Oriente Petrolero -0.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1658,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
+          <t>0x838ab1453a3e6e1dd1c01e4a10ae184c371d35fd2a8f027da12e9126060864d7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1688,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786278178</t>
+          <t>1786278182</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2.721088</t>
+          <t>16.949153</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,12 +1707,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0cd645b0a00e2cfb628e3de9be49dd41ca8da2c84af2253aee79fc9af9d6fd7f</t>
+          <t>0x22108c347bd2eed82e726fd66a4e5af989512d3b1cc616a723000e23def5b155</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1730,22 +1722,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.07986</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4725</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Oriente Petrolero -1</t>
+          <t>Oriente Petrolero -1.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1770,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xc0196d42938baf291922731a74fd66077f7bfe685c5af59ed2398d914b1cd00c</t>
+          <t>0x1c9a2c5a52d46264e6b980a01f2915cd45d668385dec869386e76a71bcb59d12</t>
         </is>
       </c>
       <c r="M13" 